--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71B4219-4AEA-4078-BC68-4177A3864DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA733AB-51BE-4758-93B5-7B59C0E70CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="219">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -644,9 +644,6 @@
     <t>AI_Confidence</t>
   </si>
   <si>
-    <t>Watch</t>
-  </si>
-  <si>
     <t>Amount</t>
   </si>
   <si>
@@ -689,16 +686,16 @@
     <t>64B.DE</t>
   </si>
   <si>
-    <t>Celestica</t>
-  </si>
-  <si>
     <t>CLS</t>
   </si>
   <si>
     <t>Part of SEC0 0,49%</t>
   </si>
   <si>
-    <t>Entry 295$, FV 365$, support 260$</t>
+    <t>CLS:XNYS</t>
+  </si>
+  <si>
+    <t>Celestica Inc.</t>
   </si>
 </sst>
 </file>
@@ -866,7 +863,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB31">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Asset_Type"/>
@@ -943,7 +940,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F32">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Yahoo_Ticker"/>
@@ -957,7 +954,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="WatchlistTable" displayName="WatchlistTable" ref="A1:J3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="WatchlistTable" displayName="WatchlistTable" ref="A1:J2">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Ticker"/>
@@ -1141,7 +1138,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1295,11 +1292,11 @@
         <v/>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M30" si="0">IFERROR(G2*H2*J2,"")</f>
+        <f t="shared" ref="M2:M31" si="0">IFERROR(G2*H2*J2,"")</f>
         <v>0</v>
       </c>
       <c r="N2" s="11" t="str">
-        <f t="shared" ref="N2:N29" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
+        <f t="shared" ref="N2:N30" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
         <v/>
       </c>
       <c r="O2" s="12">
@@ -1307,19 +1304,19 @@
         <v>0.13300607216806659</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P30" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q30" ca="1" si="3">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q31" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R30" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R31" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S17" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S18" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1389,7 +1386,7 @@
         <v>31875</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O30" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
         <v>0.45657687298649652</v>
       </c>
       <c r="P3" s="12">
@@ -1522,64 +1519,51 @@
         <v>29</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>51</v>
+        <v>218</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="H5" s="8">
-        <v>200.43</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="9">
-        <v>1</v>
-      </c>
+        <v>316.97000000000003</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="9"/>
       <c r="K5" s="8">
-        <v>377.4</v>
-      </c>
-      <c r="L5" s="13">
-        <f>IF(I5="DKK",1,IFERROR(_xludf.XLOOKUP(I5,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="11">
-        <f t="shared" si="0"/>
-        <v>30665.79</v>
-      </c>
-      <c r="N5" s="11">
-        <f t="shared" si="1"/>
-        <v>57742.2</v>
-      </c>
+        <v>316.23</v>
+      </c>
+      <c r="L5" s="13"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
       <c r="O5" s="12">
-        <f t="shared" si="6"/>
-        <v>0.88295165394402009</v>
-      </c>
-      <c r="P5" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="O5" si="7">IFERROR(K5/H5-1,"")</f>
+        <v>-2.3346057986560753E-3</v>
+      </c>
+      <c r="P5" s="12" t="str">
+        <f t="shared" ref="P5" si="8">IFERROR(L5/J5-1,"")</f>
+        <v/>
       </c>
       <c r="Q5" s="11">
-        <f t="shared" si="3"/>
-        <v>27076.409999999996</v>
-      </c>
-      <c r="R5" s="12">
-        <f t="shared" si="4"/>
-        <v>0.88295165394402031</v>
+        <f t="shared" ref="Q5" si="9">IFERROR(N5-M5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="12" t="str">
+        <f t="shared" ref="R5" si="10">IFERROR(N5/M5-1,"")</f>
+        <v/>
       </c>
       <c r="S5" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>8.0429992948366363E-2</v>
+        <f t="shared" ref="S5" ca="1" si="11">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <v>0</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="U5" s="6" t="s">
         <v>35</v>
@@ -1602,68 +1586,70 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="H6" s="8">
-        <v>45.14</v>
+        <v>200.43</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J6" s="9">
+        <v>1</v>
+      </c>
       <c r="K6" s="8">
-        <v>40</v>
-      </c>
-      <c r="L6" s="13" t="str">
-        <f ca="1">IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
+        <v>377.4</v>
+      </c>
+      <c r="L6" s="13">
+        <f>IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>30665.79</v>
+      </c>
+      <c r="N6" s="11">
+        <f t="shared" si="1"/>
+        <v>57742.2</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>-0.11386796632698271</v>
-      </c>
-      <c r="P6" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q6" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R6" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>0.88295165394402009</v>
+      </c>
+      <c r="P6" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11">
+        <f t="shared" si="3"/>
+        <v>27076.409999999996</v>
+      </c>
+      <c r="R6" s="12">
+        <f t="shared" si="4"/>
+        <v>0.88295165394402031</v>
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>8.0429992948366363E-2</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="U6" s="6" t="s">
         <v>35</v>
@@ -1686,33 +1672,33 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="H7" s="8">
-        <v>396.46</v>
+        <v>45.14</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8">
-        <v>425</v>
+        <v>40</v>
       </c>
       <c r="L7" s="13" t="str">
         <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1728,7 +1714,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>7.1987085708520526E-2</v>
+        <v>-0.11386796632698271</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1747,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="U7" s="6" t="s">
         <v>35</v>
@@ -1770,70 +1756,68 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="7">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="H8" s="8">
-        <v>406.95</v>
+        <v>396.46</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="9">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="J8" s="9"/>
       <c r="K8" s="8">
-        <v>910</v>
-      </c>
-      <c r="L8" s="13">
-        <f>IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>425</v>
+      </c>
+      <c r="L8" s="13" t="str">
+        <f ca="1">IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="0"/>
-        <v>25637.85</v>
-      </c>
-      <c r="N8" s="11">
-        <f t="shared" si="1"/>
-        <v>57330</v>
+        <v>0</v>
+      </c>
+      <c r="N8" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>1.2361469467993613</v>
-      </c>
-      <c r="P8" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="11">
-        <f t="shared" si="3"/>
-        <v>31692.15</v>
-      </c>
-      <c r="R8" s="12">
-        <f t="shared" si="4"/>
-        <v>1.2361469467993613</v>
+        <v>7.1987085708520526E-2</v>
+      </c>
+      <c r="P8" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q8" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R8" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S8" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.9855833268040424E-2</v>
+        <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="U8" s="6" t="s">
         <v>35</v>
@@ -1856,26 +1840,26 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="7">
-        <v>336</v>
+        <v>63</v>
       </c>
       <c r="H9" s="8">
-        <v>443</v>
+        <v>406.95</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>42</v>
@@ -1884,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>298</v>
+        <v>910</v>
       </c>
       <c r="L9" s="13">
         <f>IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1892,15 +1876,15 @@
       </c>
       <c r="M9" s="11">
         <f t="shared" si="0"/>
-        <v>148848</v>
+        <v>25637.85</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>100128</v>
+        <v>57330</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="6"/>
-        <v>-0.32731376975169302</v>
+        <v>1.2361469467993613</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="2"/>
@@ -1908,18 +1892,18 @@
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>-48720</v>
+        <v>31692.15</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>-0.32731376975169302</v>
+        <v>1.2361469467993613</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13946982161978635</v>
+        <v>7.9855833268040424E-2</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="U9" s="6" t="s">
         <v>35</v>
@@ -1942,26 +1926,26 @@
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7">
-        <v>18</v>
+        <v>336</v>
       </c>
       <c r="H10" s="8">
-        <v>599.5</v>
+        <v>443</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>42</v>
@@ -1970,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>846.8</v>
+        <v>298</v>
       </c>
       <c r="L10" s="13">
         <f>IF(I10="DKK",1,IFERROR(_xludf.XLOOKUP(I10,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1978,15 +1962,15 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="0"/>
-        <v>10791</v>
+        <v>148848</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>15242.4</v>
+        <v>100128</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>0.41251042535446203</v>
+        <v>-0.32731376975169302</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1994,18 +1978,18 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>4451.3999999999996</v>
+        <v>-48720</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>0.41251042535446203</v>
+        <v>-0.32731376975169302</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1231371934498158E-2</v>
+        <v>0.13946982161978635</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="U10" s="6" t="s">
         <v>35</v>
@@ -2028,59 +2012,70 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>211</v>
+        <v>72</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H11" s="8">
-        <v>110.64</v>
+        <v>599.5</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J11" s="9">
+        <v>1</v>
+      </c>
       <c r="K11" s="8">
-        <v>110.8</v>
-      </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+        <v>846.8</v>
+      </c>
+      <c r="L11" s="13">
+        <f>IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
+      <c r="M11" s="11">
+        <f t="shared" si="0"/>
+        <v>10791</v>
+      </c>
+      <c r="N11" s="11">
+        <f t="shared" si="1"/>
+        <v>15242.4</v>
+      </c>
       <c r="O11" s="12">
-        <f>IFERROR(K11/H11-1,"")</f>
-        <v>1.4461315979754641E-3</v>
-      </c>
-      <c r="P11" s="12" t="str">
-        <f>IFERROR(L11/J11-1,"")</f>
-        <v/>
+        <f t="shared" si="6"/>
+        <v>0.41251042535446203</v>
+      </c>
+      <c r="P11" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Q11" s="11">
-        <f>IFERROR(N11-M11,"")</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="12" t="str">
-        <f>IFERROR(N11/M11-1,"")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>4451.3999999999996</v>
+      </c>
+      <c r="R11" s="12">
+        <f t="shared" si="4"/>
+        <v>0.41251042535446203</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>2.1231371934498158E-2</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>35</v>
@@ -2103,60 +2098,51 @@
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
         <v>10</v>
       </c>
       <c r="H12" s="8">
-        <v>142.09</v>
+        <v>110.64</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>157.72</v>
-      </c>
-      <c r="L12" s="13" t="str">
-        <f ca="1">IF(I12="DKK",1,IFERROR(_xludf.XLOOKUP(I12,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M12" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>110.8</v>
+      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
       <c r="O12" s="12">
-        <f t="shared" si="6"/>
-        <v>0.11000070377929472</v>
+        <f>IFERROR(K12/H12-1,"")</f>
+        <v>1.4461315979754641E-3</v>
       </c>
       <c r="P12" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q12" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+        <f>IFERROR(L12/J12-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="11">
+        <f>IFERROR(N12-M12,"")</f>
+        <v>0</v>
       </c>
       <c r="R12" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f>IFERROR(N12/M12-1,"")</f>
         <v/>
       </c>
       <c r="S12" s="12">
@@ -2164,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>35</v>
@@ -2187,33 +2173,33 @@
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H13" s="8">
-        <v>414.7</v>
+        <v>142.09</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>418</v>
+        <v>157.72</v>
       </c>
       <c r="L13" s="13" t="str">
         <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2229,7 +2215,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>7.9575596816976457E-3</v>
+        <v>0.11000070377929472</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2248,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>35</v>
@@ -2271,70 +2257,68 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="H14" s="8">
-        <v>158.44</v>
+        <v>414.7</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="9">
-        <v>1</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="J14" s="9"/>
       <c r="K14" s="8">
-        <v>176.55</v>
-      </c>
-      <c r="L14" s="13">
-        <f>IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>418</v>
+      </c>
+      <c r="L14" s="13" t="str">
+        <f ca="1">IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M14" s="11">
-        <f>IFERROR(G14*H14*J14,"")</f>
-        <v>21072.52</v>
-      </c>
-      <c r="N14" s="11">
-        <f t="shared" si="1"/>
-        <v>23481.15</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>0.11430194395354709</v>
-      </c>
-      <c r="P14" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <f t="shared" si="3"/>
-        <v>2408.630000000001</v>
-      </c>
-      <c r="R14" s="12">
-        <f t="shared" si="4"/>
-        <v>0.11430194395354709</v>
+        <v>7.9575596816976457E-3</v>
+      </c>
+      <c r="P14" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q14" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R14" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S14" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2707252735772678E-2</v>
+        <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="U14" s="6" t="s">
         <v>35</v>
@@ -2357,68 +2341,70 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>212</v>
+        <v>88</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>212</v>
+        <v>89</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="H15" s="8">
-        <v>58.2</v>
+        <v>158.44</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J15" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J15" s="9">
+        <v>1</v>
+      </c>
       <c r="K15" s="8">
-        <v>58</v>
-      </c>
-      <c r="L15" s="13" t="str">
-        <f ca="1">IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
+        <v>176.55</v>
+      </c>
+      <c r="L15" s="13">
+        <f>IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
       </c>
       <c r="M15" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
+        <f>IFERROR(G15*H15*J15,"")</f>
+        <v>21072.52</v>
+      </c>
+      <c r="N15" s="11">
+        <f t="shared" si="1"/>
+        <v>23481.15</v>
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>-3.4364261168385868E-3</v>
-      </c>
-      <c r="P15" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q15" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R15" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>0.11430194395354709</v>
+      </c>
+      <c r="P15" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="11">
+        <f t="shared" si="3"/>
+        <v>2408.630000000001</v>
+      </c>
+      <c r="R15" s="12">
+        <f t="shared" si="4"/>
+        <v>0.11430194395354709</v>
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>3.2707252735772678E-2</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>35</v>
@@ -2436,40 +2422,38 @@
         <v>37</v>
       </c>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="14" t="s">
-        <v>95</v>
-      </c>
+      <c r="AA15" s="14"/>
       <c r="AB15" s="14"/>
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H16" s="8">
-        <v>46.25</v>
+        <v>58.2</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L16" s="13" t="str">
         <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2485,7 +2469,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>3.7837837837837895E-2</v>
+        <v>-3.4364261168385868E-3</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2504,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="U16" s="6" t="s">
         <v>35</v>
@@ -2522,65 +2506,67 @@
         <v>37</v>
       </c>
       <c r="Z16" s="6"/>
-      <c r="AA16" s="14"/>
+      <c r="AA16" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="AB16" s="14"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H17" s="8">
-        <v>29.05</v>
+        <v>46.25</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="L17" s="13" t="str">
         <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
         <v/>
       </c>
       <c r="M17" s="11">
-        <f>IFERROR(G17*H17*J17,"")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N17" s="11" t="str">
-        <f ca="1">IFERROR(G17*K17*L17,"")</f>
+        <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="O17" s="12">
-        <f>IFERROR(K17/H17-1,"")</f>
-        <v>-0.20826161790017217</v>
+        <f t="shared" si="6"/>
+        <v>3.7837837837837895E-2</v>
       </c>
       <c r="P17" s="12" t="str">
-        <f ca="1">IFERROR(L17/J17-1,"")</f>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="Q17" s="11" t="str">
-        <f ca="1">IFERROR(N17-M17,"")</f>
+        <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="R17" s="12" t="str">
-        <f ca="1">IFERROR(N17/M17-1,"")</f>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="S17" s="12">
@@ -2588,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>35</v>
@@ -2611,47 +2597,68 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H18" s="8">
-        <v>79.010000000000005</v>
+        <v>29.05</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8">
-        <v>79</v>
-      </c>
-      <c r="L18" s="13"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="L18" s="13" t="str">
+        <f ca="1">IF(I18="DKK",1,IFERROR(_xludf.XLOOKUP(I18,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
+      </c>
+      <c r="M18" s="11">
+        <f>IFERROR(G18*H18*J18,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="11" t="str">
+        <f ca="1">IFERROR(G18*K18*L18,"")</f>
+        <v/>
+      </c>
       <c r="O18" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.2656625743578953E-4</v>
-      </c>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
+        <f>IFERROR(K18/H18-1,"")</f>
+        <v>-0.20826161790017217</v>
+      </c>
+      <c r="P18" s="12" t="str">
+        <f ca="1">IFERROR(L18/J18-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="11" t="str">
+        <f ca="1">IFERROR(N18-M18,"")</f>
+        <v/>
+      </c>
+      <c r="R18" s="12" t="str">
+        <f ca="1">IFERROR(N18/M18-1,"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="12">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
       <c r="T18" s="6" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>35</v>
@@ -2674,68 +2681,47 @@
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="H19" s="8">
-        <v>10.71</v>
+        <v>79.010000000000005</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="L19" s="13" t="str">
-        <f ca="1">IF(I19="DKK",1,IFERROR(_xludf.XLOOKUP(I19,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M19" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="L19" s="13"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>-0.13165266106442575</v>
-      </c>
-      <c r="P19" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q19" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R19" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S19" s="12">
-        <f t="shared" ref="S19:S30" ca="1" si="7">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0</v>
-      </c>
+        <v>-1.2656625743578953E-4</v>
+      </c>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
       <c r="T19" s="6" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>35</v>
@@ -2758,33 +2744,33 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7">
-        <v>363</v>
+        <v>185</v>
       </c>
       <c r="H20" s="8">
-        <v>10</v>
+        <v>10.71</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>17</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2800,7 +2786,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>-0.13165266106442575</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2815,11 +2801,11 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ref="S20:S31" ca="1" si="12">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>35</v>
@@ -2842,33 +2828,33 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
-        <v>9</v>
+        <v>363</v>
       </c>
       <c r="H21" s="8">
-        <v>108.73</v>
+        <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="8">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="L21" s="13" t="str">
         <f ca="1">IF(I21="DKK",1,IFERROR(_xludf.XLOOKUP(I21,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2884,7 +2870,7 @@
       </c>
       <c r="O21" s="12">
         <f t="shared" si="6"/>
-        <v>-3.4305159569576027E-2</v>
+        <v>0.7</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2899,7 +2885,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2926,33 +2912,33 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
-        <v>262</v>
+        <v>9</v>
       </c>
       <c r="H22" s="8">
-        <v>8.89</v>
+        <v>108.73</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2968,7 +2954,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1001124859392577</v>
+        <v>-3.4305159569576027E-2</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2983,11 +2969,11 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>35</v>
@@ -3010,33 +2996,33 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7">
-        <v>44</v>
+        <v>262</v>
       </c>
       <c r="H23" s="8">
-        <v>57.12</v>
+        <v>8.89</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3052,7 +3038,7 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="6"/>
-        <v>-1.9607843137254832E-2</v>
+        <v>-0.1001124859392577</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3067,11 +3053,11 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>35</v>
@@ -3094,33 +3080,33 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H24" s="8">
-        <v>28.1</v>
+        <v>57.12</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3136,7 +3122,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4733096085409345E-2</v>
+        <v>-1.9607843137254832E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3151,11 +3137,11 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>35</v>
@@ -3178,33 +3164,33 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="H25" s="8">
-        <v>16.68</v>
+        <v>28.1</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3220,7 +3206,7 @@
       </c>
       <c r="O25" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28057553956834536</v>
+        <v>-7.4733096085409345E-2</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3235,11 +3221,11 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>35</v>
@@ -3262,33 +3248,33 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="H26" s="8">
-        <v>57.13</v>
+        <v>16.68</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3304,7 +3290,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-5.4787327148608456E-2</v>
+        <v>-0.28057553956834536</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3319,7 +3305,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3346,33 +3332,33 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H27" s="8">
-        <v>95.51</v>
+        <v>57.13</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3388,7 +3374,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-0.214741911841692</v>
+        <v>-5.4787327148608456E-2</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3403,11 +3389,11 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>35</v>
@@ -3430,33 +3416,33 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H28" s="8">
-        <v>77.56</v>
+        <v>95.51</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3472,7 +3458,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>5.6730273336771386E-3</v>
+        <v>-0.214741911841692</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3487,11 +3473,11 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="U28" s="6" t="s">
         <v>35</v>
@@ -3514,33 +3500,33 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H29" s="8">
-        <v>159</v>
+        <v>77.56</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="8">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="L29" s="13" t="str">
         <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3556,7 +3542,7 @@
       </c>
       <c r="O29" s="12">
         <f t="shared" si="6"/>
-        <v>5.6603773584905648E-2</v>
+        <v>5.6730273336771386E-3</v>
       </c>
       <c r="P29" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3571,14 +3557,14 @@
         <v/>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="V29" s="10" t="b">
         <v>1</v>
@@ -3598,76 +3584,74 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="6" t="s">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="H30" s="8">
-        <v>637</v>
+        <v>159</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="9">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="J30" s="9"/>
       <c r="K30" s="8">
-        <v>1662</v>
-      </c>
-      <c r="L30" s="13">
-        <f>IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>168</v>
+      </c>
+      <c r="L30" s="13" t="str">
+        <f ca="1">IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M30" s="11">
         <f t="shared" si="0"/>
-        <v>165620</v>
-      </c>
-      <c r="N30" s="11">
-        <f>IFERROR(G30*K30*L30,"")</f>
-        <v>432120</v>
+        <v>0</v>
+      </c>
+      <c r="N30" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O30" s="12">
         <f t="shared" si="6"/>
-        <v>1.609105180533752</v>
-      </c>
-      <c r="P30" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="11">
-        <f t="shared" si="3"/>
-        <v>266500</v>
-      </c>
-      <c r="R30" s="12">
-        <f t="shared" si="4"/>
-        <v>1.609105180533752</v>
+        <v>5.6603773584905648E-2</v>
+      </c>
+      <c r="P30" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q30" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R30" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S30" s="12">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.60190655279584215</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>0</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="V30" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="10" t="b">
         <v>1</v>
@@ -3682,10 +3666,96 @@
       <c r="AA30" s="14"/>
       <c r="AB30" s="14"/>
     </row>
+    <row r="31" spans="1:28">
+      <c r="A31" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="7">
+        <v>260</v>
+      </c>
+      <c r="H31" s="8">
+        <v>637</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" s="9">
+        <v>1</v>
+      </c>
+      <c r="K31" s="8">
+        <v>1662</v>
+      </c>
+      <c r="L31" s="13">
+        <f>IF(I31="DKK",1,IFERROR(_xludf.XLOOKUP(I31,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
+      <c r="M31" s="11">
+        <f t="shared" si="0"/>
+        <v>165620</v>
+      </c>
+      <c r="N31" s="11">
+        <f>IFERROR(G31*K31*L31,"")</f>
+        <v>432120</v>
+      </c>
+      <c r="O31" s="12">
+        <f t="shared" si="6"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="P31" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="11">
+        <f t="shared" si="3"/>
+        <v>266500</v>
+      </c>
+      <c r="R31" s="12">
+        <f t="shared" si="4"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="S31" s="12">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.60190655279584215</v>
+      </c>
+      <c r="T31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="U31" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="V31" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:S30">
+  <conditionalFormatting sqref="G2:S31">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -4147,7 +4217,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -4240,16 +4310,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>192</v>
@@ -4260,13 +4330,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>192</v>
@@ -4277,16 +4350,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>192</v>
@@ -4297,13 +4367,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>195</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>192</v>
@@ -4314,10 +4387,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -4331,13 +4404,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
@@ -4351,16 +4421,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>192</v>
@@ -4371,10 +4441,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
         <v>195</v>
@@ -4391,16 +4461,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
         <v>192</v>
@@ -4411,16 +4481,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>192</v>
@@ -4431,16 +4501,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
         <v>192</v>
@@ -4451,16 +4521,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>212</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
         <v>192</v>
@@ -4471,10 +4541,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>211</v>
+      </c>
+      <c r="C17" t="s">
+        <v>195</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
@@ -4488,10 +4561,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
@@ -4505,10 +4578,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
@@ -4522,10 +4595,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
@@ -4539,10 +4612,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
@@ -4556,10 +4629,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
@@ -4573,10 +4646,10 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
@@ -4590,10 +4663,10 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
@@ -4607,10 +4680,10 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
@@ -4624,10 +4697,10 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
@@ -4641,10 +4714,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
@@ -4658,10 +4731,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
@@ -4675,10 +4748,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
@@ -4692,10 +4765,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
@@ -4709,18 +4782,35 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
         <v>192</v>
       </c>
       <c r="F31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
+        <v>192</v>
+      </c>
+      <c r="F32" t="s">
         <v>181</v>
       </c>
     </row>
@@ -4735,7 +4825,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
@@ -4783,13 +4873,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s">
         <v>213</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>214</v>
-      </c>
-      <c r="C2" t="s">
-        <v>215</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -4801,43 +4891,11 @@
         <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
         <v>216</v>
       </c>
-      <c r="B3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G3">
-        <v>290</v>
-      </c>
-      <c r="H3">
-        <v>365</v>
-      </c>
-      <c r="I3">
-        <v>91</v>
-      </c>
-      <c r="J3" t="s">
-        <v>219</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:I201">
+  <conditionalFormatting sqref="G2:I200">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -4872,13 +4930,13 @@
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>145</v>
@@ -4895,14 +4953,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>63241</v>
+        <v>64127</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>63241</v>
+        <v>64127</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA733AB-51BE-4758-93B5-7B59C0E70CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F3F365-2978-4205-8AEF-F847B4D895BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="219">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -1534,7 +1534,9 @@
       <c r="H5" s="8">
         <v>316.97000000000003</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="K5" s="8">
         <v>316.23</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F3F365-2978-4205-8AEF-F847B4D895BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6923C0BB-F3E6-47CA-AED7-F3C8A91D5CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1690,10 +1690,10 @@
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H7" s="8">
-        <v>45.14</v>
+        <v>45.47</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>57</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>-0.11386796632698271</v>
+        <v>-0.1202990983065757</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2191,10 +2191,10 @@
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H13" s="8">
-        <v>142.09</v>
+        <v>140.22</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>48</v>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>0.11000070377929472</v>
+        <v>0.12480387961774353</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6923C0BB-F3E6-47CA-AED7-F3C8A91D5CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017C62C6-BA18-4FF7-B0ED-916C4714C9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.4399174697693854E-2</v>
+        <v>2.771645738024045E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>8.0429992948366363E-2</v>
+        <v>5.0208916873453177E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.9855833268040424E-2</v>
+        <v>4.9850494168131289E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13946982161978635</v>
+        <v>8.7064892378626371E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1231371934498158E-2</v>
+        <v>1.3253814273649474E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2707252735772678E-2</v>
+        <v>2.0417703316518685E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="H31" s="8">
         <v>637</v>
@@ -3706,11 +3706,11 @@
       </c>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
-        <v>165620</v>
+        <v>331240</v>
       </c>
       <c r="N31" s="11">
         <f>IFERROR(G31*K31*L31,"")</f>
-        <v>432120</v>
+        <v>864240</v>
       </c>
       <c r="O31" s="12">
         <f t="shared" si="6"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="3"/>
-        <v>266500</v>
+        <v>533000</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="4"/>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.60190655279584215</v>
+        <v>0.7514877216093806</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017C62C6-BA18-4FF7-B0ED-916C4714C9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF16D936-BF7F-4CAB-B305-F83213FA225D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.771645738024045E-2</v>
+        <v>1.9731970202403585E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.0208916873453177E-2</v>
+        <v>3.5744858661058143E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.9850494168131289E-2</v>
+        <v>3.5489689465217182E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>8.7064892378626371E-2</v>
+        <v>6.198345764474561E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>1.3253814273649474E-2</v>
+        <v>9.4356888662938485E-3</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.0417703316518685E-2</v>
+        <v>1.45358228115504E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7">
-        <v>520</v>
+        <v>800</v>
       </c>
       <c r="H31" s="8">
         <v>637</v>
@@ -3706,11 +3706,11 @@
       </c>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
-        <v>331240</v>
+        <v>509600</v>
       </c>
       <c r="N31" s="11">
         <f>IFERROR(G31*K31*L31,"")</f>
-        <v>864240</v>
+        <v>1329600</v>
       </c>
       <c r="O31" s="12">
         <f t="shared" si="6"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="3"/>
-        <v>533000</v>
+        <v>820000</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="4"/>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.7514877216093806</v>
+        <v>0.82307851234873119</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF16D936-BF7F-4CAB-B305-F83213FA225D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7976A0EA-4443-4856-AAE8-23C3A6E26751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="8">
-        <v>974</v>
+        <v>2922</v>
       </c>
       <c r="L2" s="13" t="str">
         <f ca="1">IF(I2="DKK",1,IFERROR(_xludf.XLOOKUP(I2,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>0.13300607216806659</v>
+        <v>2.3990182165041993</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
@@ -1371,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="8">
-        <v>637.5</v>
+        <v>1912.5</v>
       </c>
       <c r="L3" s="13">
         <f>IF(I3="DKK",1,IFERROR(_xludf.XLOOKUP(I3,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>31875</v>
+        <v>95625</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>0.45657687298649652</v>
+        <v>3.3697306189594896</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1395,15 +1395,15 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>9991.5</v>
+        <v>73741.5</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.45657687298649674</v>
+        <v>3.3697306189594904</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>1.9731970202403585E-2</v>
+        <v>4.3724354808564486E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="8">
-        <v>1497.8</v>
+        <v>4493.3999999999996</v>
       </c>
       <c r="L4" s="13" t="str">
         <f ca="1">IF(I4="DKK",1,IFERROR(_xludf.XLOOKUP(I4,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>0.38622291738007752</v>
+        <v>3.1586687521402323</v>
       </c>
       <c r="P4" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="8">
-        <v>316.23</v>
+        <v>948.69</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="12">
         <f t="shared" ref="O5" si="7">IFERROR(K5/H5-1,"")</f>
-        <v>-2.3346057986560753E-3</v>
+        <v>1.9929961826040317</v>
       </c>
       <c r="P5" s="12" t="str">
         <f t="shared" ref="P5" si="8">IFERROR(L5/J5-1,"")</f>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="8">
-        <v>377.4</v>
+        <v>1132.1999999999998</v>
       </c>
       <c r="L6" s="13">
         <f>IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="N6" s="11">
         <f t="shared" si="1"/>
-        <v>57742.2</v>
+        <v>173226.59999999998</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>0.88295165394402009</v>
+        <v>4.6488549618320603</v>
       </c>
       <c r="P6" s="12">
         <f t="shared" si="2"/>
@@ -1640,15 +1640,15 @@
       </c>
       <c r="Q6" s="11">
         <f t="shared" si="3"/>
-        <v>27076.409999999996</v>
+        <v>142560.80999999997</v>
       </c>
       <c r="R6" s="12">
         <f t="shared" si="4"/>
-        <v>0.88295165394402031</v>
+        <v>4.6488549618320603</v>
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5744858661058143E-2</v>
+        <v>7.9207543222810733E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="L7" s="13" t="str">
         <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1202990983065757</v>
+        <v>1.6391027050802727</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8">
-        <v>425</v>
+        <v>1275</v>
       </c>
       <c r="L8" s="13" t="str">
         <f ca="1">IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>7.1987085708520526E-2</v>
+        <v>2.2159612571255614</v>
       </c>
       <c r="P8" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1870,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>910</v>
+        <v>2730</v>
       </c>
       <c r="L9" s="13">
         <f>IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1882,11 +1882,11 @@
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>57330</v>
+        <v>171990</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="6"/>
-        <v>1.2361469467993613</v>
+        <v>5.7084408403980831</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="2"/>
@@ -1894,15 +1894,15 @@
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>31692.15</v>
+        <v>146352.15</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>1.2361469467993613</v>
+        <v>5.708440840398084</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5489689465217182E-2</v>
+        <v>7.8642110154509864E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1956,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>298</v>
+        <v>894</v>
       </c>
       <c r="L10" s="13">
         <f>IF(I10="DKK",1,IFERROR(_xludf.XLOOKUP(I10,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1968,11 +1968,11 @@
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>100128</v>
+        <v>300384</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>-0.32731376975169302</v>
+        <v>1.0180586907449212</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1980,15 +1980,15 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>-48720</v>
+        <v>151536</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>-0.32731376975169302</v>
+        <v>1.0180586907449212</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>6.198345764474561E-2</v>
+        <v>0.13735002974970809</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2042,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="8">
-        <v>846.8</v>
+        <v>2540.3999999999996</v>
       </c>
       <c r="L11" s="13">
         <f>IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>15242.4</v>
+        <v>45727.199999999997</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
-        <v>0.41251042535446203</v>
+        <v>3.2375312760633852</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="2"/>
@@ -2066,15 +2066,15 @@
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>4451.3999999999996</v>
+        <v>34936.199999999997</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="4"/>
-        <v>0.41251042535446203</v>
+        <v>3.2375312760633861</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>9.4356888662938485E-3</v>
+        <v>2.0908677826951005E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2126,14 +2126,14 @@
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>110.8</v>
+        <v>332.4</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="12">
         <f>IFERROR(K12/H12-1,"")</f>
-        <v>1.4461315979754641E-3</v>
+        <v>2.0043383947939262</v>
       </c>
       <c r="P12" s="12" t="str">
         <f>IFERROR(L12/J12-1,"")</f>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>157.72</v>
+        <v>473.15999999999997</v>
       </c>
       <c r="L13" s="13" t="str">
         <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>0.12480387961774353</v>
+        <v>2.3744116388532306</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="8">
-        <v>418</v>
+        <v>1254</v>
       </c>
       <c r="L14" s="13" t="str">
         <f ca="1">IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>7.9575596816976457E-3</v>
+        <v>2.0238726790450929</v>
       </c>
       <c r="P14" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="8">
-        <v>176.55</v>
+        <v>529.65000000000009</v>
       </c>
       <c r="L15" s="13">
         <f>IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>23481.15</v>
+        <v>70443.450000000012</v>
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>0.11430194395354709</v>
+        <v>2.3429058318606417</v>
       </c>
       <c r="P15" s="12">
         <f t="shared" si="2"/>
@@ -2395,15 +2395,15 @@
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="3"/>
-        <v>2408.630000000001</v>
+        <v>49370.930000000008</v>
       </c>
       <c r="R15" s="12">
         <f t="shared" si="4"/>
-        <v>0.11430194395354709</v>
+        <v>2.3429058318606417</v>
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>1.45358228115504E-2</v>
+        <v>3.2210137534529386E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="L16" s="13" t="str">
         <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>-3.4364261168385868E-3</v>
+        <v>1.9896907216494846</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="L17" s="13" t="str">
         <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O17" s="12">
         <f t="shared" si="6"/>
-        <v>3.7837837837837895E-2</v>
+        <v>2.1135135135135137</v>
       </c>
       <c r="P17" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="L18" s="13" t="str">
         <f ca="1">IF(I18="DKK",1,IFERROR(_xludf.XLOOKUP(I18,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="O18" s="12">
         <f>IFERROR(K18/H18-1,"")</f>
-        <v>-0.20826161790017217</v>
+        <v>1.3752151462994835</v>
       </c>
       <c r="P18" s="12" t="str">
         <f ca="1">IFERROR(L18/J18-1,"")</f>
@@ -2709,14 +2709,14 @@
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="L19" s="13"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>-1.2656625743578953E-4</v>
+        <v>1.9996203012276923</v>
       </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="11"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>9.3000000000000007</v>
+        <v>27.900000000000002</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>-0.13165266106442575</v>
+        <v>1.6050420168067228</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="8">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="L21" s="13" t="str">
         <f ca="1">IF(I21="DKK",1,IFERROR(_xludf.XLOOKUP(I21,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="O21" s="12">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>105</v>
+        <v>315</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-3.4305159569576027E-2</v>
+        <v>1.8970845212912719</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1001124859392577</v>
+        <v>1.6996625421822271</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-1.9607843137254832E-2</v>
+        <v>1.9411764705882355</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="O25" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4733096085409345E-2</v>
+        <v>1.7758007117437722</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28057553956834536</v>
+        <v>1.1582733812949639</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-5.4787327148608456E-2</v>
+        <v>1.8356380185541745</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>-0.214741911841692</v>
+        <v>1.355774264474924</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="8">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="L29" s="13" t="str">
         <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="O29" s="12">
         <f t="shared" si="6"/>
-        <v>5.6730273336771386E-3</v>
+        <v>2.0170190820010312</v>
       </c>
       <c r="P29" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="8">
-        <v>168</v>
+        <v>504</v>
       </c>
       <c r="L30" s="13" t="str">
         <f ca="1">IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O30" s="12">
         <f t="shared" si="6"/>
-        <v>5.6603773584905648E-2</v>
+        <v>2.1698113207547172</v>
       </c>
       <c r="P30" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.82307851234873119</v>
+        <v>0.60795714670292644</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7976A0EA-4443-4856-AAE8-23C3A6E26751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD198A93-3351-4CC0-B136-E5527D85C1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.3724354808564486E-2</v>
+        <v>7.4155715370007938E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.9207543222810733E-2</v>
+        <v>0.13433456150707676</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.8642110154509864E-2</v>
+        <v>0.13337559724431547</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13735002974970809</v>
+        <v>0.23294316764135389</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.0908677826951005E-2</v>
+        <v>3.5460739637829301E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2210137534529386E-2</v>
+        <v>5.4627811010524302E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7">
-        <v>800</v>
+        <v>260</v>
       </c>
       <c r="H31" s="8">
         <v>637</v>
@@ -3706,11 +3706,11 @@
       </c>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
-        <v>509600</v>
+        <v>165620</v>
       </c>
       <c r="N31" s="11">
         <f>IFERROR(G31*K31*L31,"")</f>
-        <v>1329600</v>
+        <v>432120</v>
       </c>
       <c r="O31" s="12">
         <f t="shared" si="6"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="3"/>
-        <v>820000</v>
+        <v>266500</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="4"/>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.60795714670292644</v>
+        <v>0.33510240758889237</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD198A93-3351-4CC0-B136-E5527D85C1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D46BE7F-80DE-40DF-9445-B05316D9A6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="8">
-        <v>2922</v>
+        <v>974</v>
       </c>
       <c r="L2" s="13" t="str">
         <f ca="1">IF(I2="DKK",1,IFERROR(_xludf.XLOOKUP(I2,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>2.3990182165041993</v>
+        <v>0.13300607216806659</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
@@ -1371,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="8">
-        <v>1912.5</v>
+        <v>637.5</v>
       </c>
       <c r="L3" s="13">
         <f>IF(I3="DKK",1,IFERROR(_xludf.XLOOKUP(I3,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>95625</v>
+        <v>31875</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>3.3697306189594896</v>
+        <v>0.45657687298649652</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1395,15 +1395,15 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>73741.5</v>
+        <v>9991.5</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>3.3697306189594904</v>
+        <v>0.45657687298649674</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.4155715370007938E-2</v>
+        <v>4.4399174697693854E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="8">
-        <v>4493.3999999999996</v>
+        <v>1497.8</v>
       </c>
       <c r="L4" s="13" t="str">
         <f ca="1">IF(I4="DKK",1,IFERROR(_xludf.XLOOKUP(I4,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>3.1586687521402323</v>
+        <v>0.38622291738007752</v>
       </c>
       <c r="P4" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="8">
-        <v>948.69</v>
+        <v>316.23</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="12">
         <f t="shared" ref="O5" si="7">IFERROR(K5/H5-1,"")</f>
-        <v>1.9929961826040317</v>
+        <v>-2.3346057986560753E-3</v>
       </c>
       <c r="P5" s="12" t="str">
         <f t="shared" ref="P5" si="8">IFERROR(L5/J5-1,"")</f>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="8">
-        <v>1132.1999999999998</v>
+        <v>377.4</v>
       </c>
       <c r="L6" s="13">
         <f>IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="N6" s="11">
         <f t="shared" si="1"/>
-        <v>173226.59999999998</v>
+        <v>57742.2</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>4.6488549618320603</v>
+        <v>0.88295165394402009</v>
       </c>
       <c r="P6" s="12">
         <f t="shared" si="2"/>
@@ -1640,15 +1640,15 @@
       </c>
       <c r="Q6" s="11">
         <f t="shared" si="3"/>
-        <v>142560.80999999997</v>
+        <v>27076.409999999996</v>
       </c>
       <c r="R6" s="12">
         <f t="shared" si="4"/>
-        <v>4.6488549618320603</v>
+        <v>0.88295165394402031</v>
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13433456150707676</v>
+        <v>8.0429992948366363E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="L7" s="13" t="str">
         <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>1.6391027050802727</v>
+        <v>-0.1202990983065757</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8">
-        <v>1275</v>
+        <v>425</v>
       </c>
       <c r="L8" s="13" t="str">
         <f ca="1">IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>2.2159612571255614</v>
+        <v>7.1987085708520526E-2</v>
       </c>
       <c r="P8" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1870,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>2730</v>
+        <v>910</v>
       </c>
       <c r="L9" s="13">
         <f>IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1882,11 +1882,11 @@
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>171990</v>
+        <v>57330</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="6"/>
-        <v>5.7084408403980831</v>
+        <v>1.2361469467993613</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="2"/>
@@ -1894,15 +1894,15 @@
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>146352.15</v>
+        <v>31692.15</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>5.708440840398084</v>
+        <v>1.2361469467993613</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13337559724431547</v>
+        <v>7.9855833268040424E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1956,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>894</v>
+        <v>298</v>
       </c>
       <c r="L10" s="13">
         <f>IF(I10="DKK",1,IFERROR(_xludf.XLOOKUP(I10,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1968,11 +1968,11 @@
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>300384</v>
+        <v>100128</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>1.0180586907449212</v>
+        <v>-0.32731376975169302</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1980,15 +1980,15 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>151536</v>
+        <v>-48720</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>1.0180586907449212</v>
+        <v>-0.32731376975169302</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.23294316764135389</v>
+        <v>0.13946982161978635</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2042,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="8">
-        <v>2540.3999999999996</v>
+        <v>846.8</v>
       </c>
       <c r="L11" s="13">
         <f>IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>45727.199999999997</v>
+        <v>15242.4</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
-        <v>3.2375312760633852</v>
+        <v>0.41251042535446203</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="2"/>
@@ -2066,15 +2066,15 @@
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>34936.199999999997</v>
+        <v>4451.3999999999996</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="4"/>
-        <v>3.2375312760633861</v>
+        <v>0.41251042535446203</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5460739637829301E-2</v>
+        <v>2.1231371934498158E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2126,14 +2126,14 @@
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>332.4</v>
+        <v>110.8</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="12">
         <f>IFERROR(K12/H12-1,"")</f>
-        <v>2.0043383947939262</v>
+        <v>1.4461315979754641E-3</v>
       </c>
       <c r="P12" s="12" t="str">
         <f>IFERROR(L12/J12-1,"")</f>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>473.15999999999997</v>
+        <v>157.72</v>
       </c>
       <c r="L13" s="13" t="str">
         <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>2.3744116388532306</v>
+        <v>0.12480387961774353</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="8">
-        <v>1254</v>
+        <v>418</v>
       </c>
       <c r="L14" s="13" t="str">
         <f ca="1">IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>2.0238726790450929</v>
+        <v>7.9575596816976457E-3</v>
       </c>
       <c r="P14" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="8">
-        <v>529.65000000000009</v>
+        <v>176.55</v>
       </c>
       <c r="L15" s="13">
         <f>IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>70443.450000000012</v>
+        <v>23481.15</v>
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>2.3429058318606417</v>
+        <v>0.11430194395354709</v>
       </c>
       <c r="P15" s="12">
         <f t="shared" si="2"/>
@@ -2395,15 +2395,15 @@
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="3"/>
-        <v>49370.930000000008</v>
+        <v>2408.630000000001</v>
       </c>
       <c r="R15" s="12">
         <f t="shared" si="4"/>
-        <v>2.3429058318606417</v>
+        <v>0.11430194395354709</v>
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.4627811010524302E-2</v>
+        <v>3.2707252735772678E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="L16" s="13" t="str">
         <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>1.9896907216494846</v>
+        <v>-3.4364261168385868E-3</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="L17" s="13" t="str">
         <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O17" s="12">
         <f t="shared" si="6"/>
-        <v>2.1135135135135137</v>
+        <v>3.7837837837837895E-2</v>
       </c>
       <c r="P17" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="L18" s="13" t="str">
         <f ca="1">IF(I18="DKK",1,IFERROR(_xludf.XLOOKUP(I18,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="O18" s="12">
         <f>IFERROR(K18/H18-1,"")</f>
-        <v>1.3752151462994835</v>
+        <v>-0.20826161790017217</v>
       </c>
       <c r="P18" s="12" t="str">
         <f ca="1">IFERROR(L18/J18-1,"")</f>
@@ -2709,14 +2709,14 @@
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="L19" s="13"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>1.9996203012276923</v>
+        <v>-1.2656625743578953E-4</v>
       </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="11"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>27.900000000000002</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>1.6050420168067228</v>
+        <v>-0.13165266106442575</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="8">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="L21" s="13" t="str">
         <f ca="1">IF(I21="DKK",1,IFERROR(_xludf.XLOOKUP(I21,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="O21" s="12">
         <f t="shared" si="6"/>
-        <v>4.0999999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>315</v>
+        <v>105</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>1.8970845212912719</v>
+        <v>-3.4305159569576027E-2</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="6"/>
-        <v>1.6996625421822271</v>
+        <v>-0.1001124859392577</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>1.9411764705882355</v>
+        <v>-1.9607843137254832E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="O25" s="12">
         <f t="shared" si="6"/>
-        <v>1.7758007117437722</v>
+        <v>-7.4733096085409345E-2</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>1.1582733812949639</v>
+        <v>-0.28057553956834536</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>1.8356380185541745</v>
+        <v>-5.4787327148608456E-2</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>1.355774264474924</v>
+        <v>-0.214741911841692</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="8">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="L29" s="13" t="str">
         <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="O29" s="12">
         <f t="shared" si="6"/>
-        <v>2.0170190820010312</v>
+        <v>5.6730273336771386E-3</v>
       </c>
       <c r="P29" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="8">
-        <v>504</v>
+        <v>168</v>
       </c>
       <c r="L30" s="13" t="str">
         <f ca="1">IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O30" s="12">
         <f t="shared" si="6"/>
-        <v>2.1698113207547172</v>
+        <v>5.6603773584905648E-2</v>
       </c>
       <c r="P30" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.33510240758889237</v>
+        <v>0.60190655279584215</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D46BE7F-80DE-40DF-9445-B05316D9A6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00111038-AF7B-48A8-ADEE-0D9587C31C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.4399174697693854E-2</v>
+        <v>2.771645738024045E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>8.0429992948366363E-2</v>
+        <v>5.0208916873453177E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.9855833268040424E-2</v>
+        <v>4.9850494168131289E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13946982161978635</v>
+        <v>8.7064892378626371E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1231371934498158E-2</v>
+        <v>1.3253814273649474E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2707252735772678E-2</v>
+        <v>2.0417703316518685E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3686,7 +3686,8 @@
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7">
-        <v>260</v>
+        <f>260*2</f>
+        <v>520</v>
       </c>
       <c r="H31" s="8">
         <v>637</v>
@@ -3706,11 +3707,11 @@
       </c>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
-        <v>165620</v>
+        <v>331240</v>
       </c>
       <c r="N31" s="11">
         <f>IFERROR(G31*K31*L31,"")</f>
-        <v>432120</v>
+        <v>864240</v>
       </c>
       <c r="O31" s="12">
         <f t="shared" si="6"/>
@@ -3722,7 +3723,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="3"/>
-        <v>266500</v>
+        <v>533000</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="4"/>
@@ -3730,7 +3731,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.60190655279584215</v>
+        <v>0.7514877216093806</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00111038-AF7B-48A8-ADEE-0D9587C31C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E112E77-4516-4D44-B27E-130CAF75638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.771645738024045E-2</v>
+        <v>2.3332866675999812E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.0208916873453177E-2</v>
+        <v>4.2267954640907178E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.9850494168131289E-2</v>
+        <v>4.196621949913943E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>8.7064892378626371E-2</v>
+        <v>7.3294847828533627E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>1.3253814273649474E-2</v>
+        <v>1.115761214187481E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.0417703316518685E-2</v>
+        <v>1.7188471916836173E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3686,8 +3686,8 @@
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7">
-        <f>260*2</f>
-        <v>520</v>
+        <f>260*2.5</f>
+        <v>650</v>
       </c>
       <c r="H31" s="8">
         <v>637</v>
@@ -3707,11 +3707,11 @@
       </c>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
-        <v>331240</v>
+        <v>414050</v>
       </c>
       <c r="N31" s="11">
         <f>IFERROR(G31*K31*L31,"")</f>
-        <v>864240</v>
+        <v>1080300</v>
       </c>
       <c r="O31" s="12">
         <f t="shared" si="6"/>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="3"/>
-        <v>533000</v>
+        <v>666250</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="4"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.7514877216093806</v>
+        <v>0.79079202729670894</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8001_{C8BF0FB8-00FD-4C74-BBE8-EE4045D163E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C5166E-D546-4DC6-B6B5-534EED7D53DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-53100" yWindow="3495" windowWidth="19185" windowHeight="11265" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -3350,10 +3350,10 @@
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H27" s="8">
-        <v>57.13</v>
+        <v>58.71</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-5.4787327148608456E-2</v>
+        <v>-8.0224833929483874E-2</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4956,14 +4956,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>64127</v>
+        <v>70042</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>64127</v>
+        <v>70042</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C5166E-D546-4DC6-B6B5-534EED7D53DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E081AAC6-B9AC-4C9B-BEAE-E7CD6C05DF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-53100" yWindow="3495" windowWidth="19185" windowHeight="11265" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="870" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1278,7 +1278,7 @@
         <v>47</v>
       </c>
       <c r="H2" s="8">
-        <v>859.66</v>
+        <v>858.39</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>33</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>0.13300607216806659</v>
+        <v>0.13468237048427878</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
@@ -1362,7 +1362,7 @@
         <v>50</v>
       </c>
       <c r="H3" s="8">
-        <v>437.67</v>
+        <v>436.48</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>42</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="M3" s="11">
         <f t="shared" si="0"/>
-        <v>21883.5</v>
+        <v>21824</v>
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>0.45657687298649652</v>
+        <v>0.46054802052785915</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>9991.5</v>
+        <v>10051</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.45657687298649674</v>
+        <v>0.46054802052785915</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -1777,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="8">
-        <v>396.46</v>
+        <v>394.77</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>48</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>7.1987085708520526E-2</v>
+        <v>7.6576234262988541E-2</v>
       </c>
       <c r="P8" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1861,7 +1861,7 @@
         <v>63</v>
       </c>
       <c r="H9" s="8">
-        <v>406.95</v>
+        <v>405.68</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>42</v>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="M9" s="11">
         <f t="shared" si="0"/>
-        <v>25637.85</v>
+        <v>25557.84</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O9" s="12">
         <f t="shared" si="6"/>
-        <v>1.2361469467993613</v>
+        <v>1.2431473082232301</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="2"/>
@@ -1894,11 +1894,11 @@
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>31692.15</v>
+        <v>31772.16</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>1.2361469467993613</v>
+        <v>1.2431473082232301</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -2194,7 +2194,7 @@
         <v>15</v>
       </c>
       <c r="H13" s="8">
-        <v>140.22</v>
+        <v>139.62</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>48</v>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>0.12480387961774353</v>
+        <v>0.12963758773814638</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2362,7 +2362,7 @@
         <v>133</v>
       </c>
       <c r="H15" s="8">
-        <v>158.44</v>
+        <v>155.74</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>42</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M15" s="11">
         <f>IFERROR(G15*H15*J15,"")</f>
-        <v>21072.52</v>
+        <v>20713.420000000002</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>0.11430194395354709</v>
+        <v>0.13362013612430967</v>
       </c>
       <c r="P15" s="12">
         <f t="shared" si="2"/>
@@ -2395,11 +2395,11 @@
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="3"/>
-        <v>2408.630000000001</v>
+        <v>2767.7299999999996</v>
       </c>
       <c r="R15" s="12">
         <f t="shared" si="4"/>
-        <v>0.11430194395354709</v>
+        <v>0.13362013612430967</v>
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -2448,7 +2448,7 @@
         <v>27</v>
       </c>
       <c r="H16" s="8">
-        <v>58.2</v>
+        <v>57.93</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>57</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>-3.4364261168385868E-3</v>
+        <v>1.2083549110997183E-3</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2534,7 +2534,7 @@
         <v>39</v>
       </c>
       <c r="H17" s="8">
-        <v>46.25</v>
+        <v>46.039000000000001</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>48</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O17" s="12">
         <f t="shared" si="6"/>
-        <v>3.7837837837837895E-2</v>
+        <v>4.2594322205086854E-2</v>
       </c>
       <c r="P17" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2618,7 +2618,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="8">
-        <v>29.05</v>
+        <v>28.96</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>48</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="O18" s="12">
         <f>IFERROR(K18/H18-1,"")</f>
-        <v>-0.20826161790017217</v>
+        <v>-0.20580110497237569</v>
       </c>
       <c r="P18" s="12" t="str">
         <f ca="1">IFERROR(L18/J18-1,"")</f>
@@ -2702,7 +2702,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="8">
-        <v>79.010000000000005</v>
+        <v>78.83</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
@@ -2716,7 +2716,7 @@
       <c r="N19" s="11"/>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>-1.2656625743578953E-4</v>
+        <v>2.1565393885576434E-3</v>
       </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="11"/>
@@ -2765,7 +2765,7 @@
         <v>185</v>
       </c>
       <c r="H20" s="8">
-        <v>10.71</v>
+        <v>10.62</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>48</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>-0.13165266106442575</v>
+        <v>-0.12429378531073432</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3101,7 +3101,7 @@
         <v>44</v>
       </c>
       <c r="H24" s="8">
-        <v>57.12</v>
+        <v>56.9</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-1.9607843137254832E-2</v>
+        <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3269,7 +3269,7 @@
         <v>161</v>
       </c>
       <c r="H26" s="8">
-        <v>16.68</v>
+        <v>16.59</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28057553956834536</v>
+        <v>-0.27667269439421338</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3353,7 +3353,7 @@
         <v>16</v>
       </c>
       <c r="H27" s="8">
-        <v>58.71</v>
+        <v>58.1</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-8.0224833929483874E-2</v>
+        <v>-7.056798623063687E-2</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3437,7 +3437,7 @@
         <v>15</v>
       </c>
       <c r="H28" s="8">
-        <v>95.51</v>
+        <v>95.08</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>48</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>-0.214741911841692</v>
+        <v>-0.2111905763567522</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4956,14 +4956,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>70042</v>
+        <v>77064</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>70042</v>
+        <v>77064</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E081AAC6-B9AC-4C9B-BEAE-E7CD6C05DF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE26328D-3417-45EA-9B22-86B7C7A348DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="870" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1359,10 +1359,10 @@
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="7">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="H3" s="8">
-        <v>436.48</v>
+        <v>493.03</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>42</v>
@@ -1379,15 +1379,15 @@
       </c>
       <c r="M3" s="11">
         <f t="shared" si="0"/>
-        <v>21824</v>
+        <v>31553.919999999998</v>
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>31875</v>
+        <v>40800</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>0.46054802052785915</v>
+        <v>0.29302476522726817</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1395,15 +1395,15 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>10051</v>
+        <v>9246.0800000000017</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.46054802052785915</v>
+        <v>0.29302476522726817</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.4399174697693854E-2</v>
+        <v>5.6961239342541645E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1604,10 +1604,10 @@
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="H6" s="8">
-        <v>200.43</v>
+        <v>212.15</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>42</v>
@@ -1624,15 +1624,15 @@
       </c>
       <c r="M6" s="11">
         <f t="shared" si="0"/>
-        <v>30665.79</v>
+        <v>26518.75</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="1"/>
-        <v>57742.2</v>
+        <v>47175</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>0.88295165394402009</v>
+        <v>0.77893000235682286</v>
       </c>
       <c r="P6" s="12">
         <f t="shared" si="2"/>
@@ -1640,15 +1640,15 @@
       </c>
       <c r="Q6" s="11">
         <f t="shared" si="3"/>
-        <v>27076.409999999996</v>
+        <v>20656.25</v>
       </c>
       <c r="R6" s="12">
         <f t="shared" si="4"/>
-        <v>0.88295165394402031</v>
+        <v>0.77893000235682308</v>
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>8.0429992948366363E-2</v>
+        <v>6.586143298981377E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.9855833268040424E-2</v>
+        <v>8.0038917929115508E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13946982161978635</v>
+        <v>0.13978958266887279</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1231371934498158E-2</v>
+        <v>2.1280048886146E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2707252735772678E-2</v>
+        <v>3.2782240323238281E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.60190655279584215</v>
+        <v>0.60328653786027198</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE26328D-3417-45EA-9B22-86B7C7A348DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0936A88C-A57B-4DAF-97C0-022597AADD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4910" yWindow="0" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -2699,10 +2699,10 @@
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H19" s="8">
-        <v>78.83</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
@@ -2716,7 +2716,7 @@
       <c r="N19" s="11"/>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>2.1565393885576434E-3</v>
+        <v>-8.1607030759573984E-3</v>
       </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="11"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0936A88C-A57B-4DAF-97C0-022597AADD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFAC2DD-FCD6-41BC-BE6F-DFE3B616836C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4910" yWindow="0" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="222">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -696,6 +696,15 @@
   </si>
   <si>
     <t>Celestica Inc.</t>
+  </si>
+  <si>
+    <t>A030</t>
+  </si>
+  <si>
+    <t>Vanguard FTSE All-World High Dvd Yield UCITS ETF</t>
+  </si>
+  <si>
+    <t>VGWD.DE</t>
   </si>
 </sst>
 </file>
@@ -863,7 +872,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB32">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Asset_Type"/>
@@ -940,7 +949,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F33">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Yahoo_Ticker"/>
@@ -1138,7 +1147,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1292,7 +1301,7 @@
         <v/>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M31" si="0">IFERROR(G2*H2*J2,"")</f>
+        <f t="shared" ref="M2:M32" si="0">IFERROR(G2*H2*J2,"")</f>
         <v>0</v>
       </c>
       <c r="N2" s="11" t="str">
@@ -1304,19 +1313,19 @@
         <v>0.13468237048427878</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P32" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q31" ca="1" si="3">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q32" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R31" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R32" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S18" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S18" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$503,$W$2:$W$503,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1386,7 +1395,7 @@
         <v>40800</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O32" si="6">IFERROR(K3/H3-1,"")</f>
         <v>0.29302476522726817</v>
       </c>
       <c r="P3" s="12">
@@ -1561,7 +1570,7 @@
         <v/>
       </c>
       <c r="S5" s="12">
-        <f t="shared" ref="S5" ca="1" si="11">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ref="S5" ca="1" si="11">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$503,$W$2:$W$503,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -2803,7 +2812,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ref="S20:S31" ca="1" si="12">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ref="S20:S32" ca="1" si="12">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$503,$W$2:$W$503,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -3602,17 +3611,17 @@
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H30" s="8">
-        <v>159</v>
+        <v>166.35</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="8">
-        <v>168</v>
+        <v>175.52</v>
       </c>
       <c r="L30" s="13" t="str">
         <f ca="1">IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3628,7 +3637,7 @@
       </c>
       <c r="O30" s="12">
         <f t="shared" si="6"/>
-        <v>5.6603773584905648E-2</v>
+        <v>5.5124737000300739E-2</v>
       </c>
       <c r="P30" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3673,74 +3682,56 @@
         <v>207</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>141</v>
+        <v>220</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7">
-        <f>260</f>
-        <v>260</v>
+        <v>17</v>
       </c>
       <c r="H31" s="8">
-        <v>637</v>
+        <v>80.75</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" s="9">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="J31" s="9"/>
       <c r="K31" s="8">
-        <v>1662</v>
-      </c>
-      <c r="L31" s="13">
-        <f>IF(I31="DKK",1,IFERROR(_xludf.XLOOKUP(I31,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
-      </c>
+        <v>80.75</v>
+      </c>
+      <c r="L31" s="13"/>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
-        <v>165620</v>
-      </c>
-      <c r="N31" s="11">
-        <f>IFERROR(G31*K31*L31,"")</f>
-        <v>432120</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N31" s="11"/>
       <c r="O31" s="12">
         <f t="shared" si="6"/>
-        <v>1.609105180533752</v>
-      </c>
-      <c r="P31" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="11">
-        <f t="shared" si="3"/>
-        <v>266500</v>
-      </c>
-      <c r="R31" s="12">
-        <f t="shared" si="4"/>
-        <v>1.609105180533752</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="12"/>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="12"/>
-        <v>0.60328653786027198</v>
+        <v>0</v>
       </c>
       <c r="T31" s="6" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="U31" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="V31" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="10" t="b">
         <v>1</v>
@@ -3755,10 +3746,97 @@
       <c r="AA31" s="14"/>
       <c r="AB31" s="14"/>
     </row>
+    <row r="32" spans="1:28">
+      <c r="A32" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="7">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="H32" s="8">
+        <v>637</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="9">
+        <v>1</v>
+      </c>
+      <c r="K32" s="8">
+        <v>1662</v>
+      </c>
+      <c r="L32" s="13">
+        <f>IF(I32="DKK",1,IFERROR(_xludf.XLOOKUP(I32,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
+      <c r="M32" s="11">
+        <f t="shared" si="0"/>
+        <v>165620</v>
+      </c>
+      <c r="N32" s="11">
+        <f>IFERROR(G32*K32*L32,"")</f>
+        <v>432120</v>
+      </c>
+      <c r="O32" s="12">
+        <f t="shared" si="6"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="P32" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11">
+        <f t="shared" si="3"/>
+        <v>266500</v>
+      </c>
+      <c r="R32" s="12">
+        <f t="shared" si="4"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="S32" s="12">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.60328653786027198</v>
+      </c>
+      <c r="T32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="U32" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="V32" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:S31">
+  <conditionalFormatting sqref="G2:S32">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -4220,7 +4298,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -4802,18 +4880,35 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
         <v>192</v>
       </c>
       <c r="F32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" t="s">
         <v>181</v>
       </c>
     </row>
@@ -4956,14 +5051,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>77064</v>
+        <v>66709</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>77064</v>
+        <v>66709</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFAC2DD-FCD6-41BC-BE6F-DFE3B616836C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994C77B5-3B73-435D-BB07-1C1148A6F164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="219">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -368,12 +368,6 @@
     <t>A019</t>
   </si>
   <si>
-    <t>iShares MSCI Korea UCITS ETF</t>
-  </si>
-  <si>
-    <t>IQQK.DE</t>
-  </si>
-  <si>
     <t>A020</t>
   </si>
   <si>
@@ -696,9 +690,6 @@
   </si>
   <si>
     <t>Celestica Inc.</t>
-  </si>
-  <si>
-    <t>A030</t>
   </si>
   <si>
     <t>Vanguard FTSE All-World High Dvd Yield UCITS ETF</t>
@@ -872,7 +863,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB31">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Asset_Type"/>
@@ -949,7 +940,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F32">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Yahoo_Ticker"/>
@@ -1147,7 +1138,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1301,11 +1292,11 @@
         <v/>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M32" si="0">IFERROR(G2*H2*J2,"")</f>
+        <f t="shared" ref="M2:M31" si="0">IFERROR(G2*H2*J2,"")</f>
         <v>0</v>
       </c>
       <c r="N2" s="11" t="str">
-        <f t="shared" ref="N2:N30" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
+        <f t="shared" ref="N2:N29" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
         <v/>
       </c>
       <c r="O2" s="12">
@@ -1313,19 +1304,19 @@
         <v>0.13468237048427878</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P32" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q32" ca="1" si="3">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q31" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R32" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R31" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S18" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$503,$W$2:$W$503,TRUE),0),0)</f>
+        <f ca="1">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1395,7 +1386,7 @@
         <v>40800</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O32" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O31" si="5">IFERROR(K3/H3-1,"")</f>
         <v>0.29302476522726817</v>
       </c>
       <c r="P3" s="12">
@@ -1411,7 +1402,7 @@
         <v>0.29302476522726817</v>
       </c>
       <c r="S3" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>5.6961239342541645E-2</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1479,7 +1470,7 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.38622291738007752</v>
       </c>
       <c r="P4" s="12" t="str">
@@ -1495,7 +1486,7 @@
         <v/>
       </c>
       <c r="S4" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1528,13 +1519,13 @@
         <v>29</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7">
@@ -1554,23 +1545,23 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="12">
-        <f t="shared" ref="O5" si="7">IFERROR(K5/H5-1,"")</f>
+        <f t="shared" ref="O5" si="6">IFERROR(K5/H5-1,"")</f>
         <v>-2.3346057986560753E-3</v>
       </c>
       <c r="P5" s="12" t="str">
-        <f t="shared" ref="P5" si="8">IFERROR(L5/J5-1,"")</f>
+        <f t="shared" ref="P5" si="7">IFERROR(L5/J5-1,"")</f>
         <v/>
       </c>
       <c r="Q5" s="11">
-        <f t="shared" ref="Q5" si="9">IFERROR(N5-M5,"")</f>
+        <f t="shared" ref="Q5" si="8">IFERROR(N5-M5,"")</f>
         <v>0</v>
       </c>
       <c r="R5" s="12" t="str">
-        <f t="shared" ref="R5" si="10">IFERROR(N5/M5-1,"")</f>
+        <f t="shared" ref="R5" si="9">IFERROR(N5/M5-1,"")</f>
         <v/>
       </c>
       <c r="S5" s="12">
-        <f t="shared" ref="S5" ca="1" si="11">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$503,$W$2:$W$503,TRUE),0),0)</f>
+        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1640,7 +1631,7 @@
         <v>47175</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.77893000235682286</v>
       </c>
       <c r="P6" s="12">
@@ -1656,7 +1647,7 @@
         <v>0.77893000235682308</v>
       </c>
       <c r="S6" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>6.586143298981377E-2</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1724,7 +1715,7 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.1202990983065757</v>
       </c>
       <c r="P7" s="12" t="str">
@@ -1740,7 +1731,7 @@
         <v/>
       </c>
       <c r="S7" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1808,7 +1799,7 @@
         <v/>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.6576234262988541E-2</v>
       </c>
       <c r="P8" s="12" t="str">
@@ -1824,7 +1815,7 @@
         <v/>
       </c>
       <c r="S8" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1894,7 +1885,7 @@
         <v>57330</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2431473082232301</v>
       </c>
       <c r="P9" s="12">
@@ -1910,7 +1901,7 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>8.0038917929115508E-2</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1980,7 +1971,7 @@
         <v>100128</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.32731376975169302</v>
       </c>
       <c r="P10" s="12">
@@ -1996,7 +1987,7 @@
         <v>-0.32731376975169302</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0.13978958266887279</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -2066,7 +2057,7 @@
         <v>15242.4</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.41251042535446203</v>
       </c>
       <c r="P11" s="12">
@@ -2082,7 +2073,7 @@
         <v>0.41251042535446203</v>
       </c>
       <c r="S11" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>2.1280048886146E-2</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2115,13 +2106,13 @@
         <v>29</v>
       </c>
       <c r="C12" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="E12" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
@@ -2157,7 +2148,7 @@
         <v/>
       </c>
       <c r="S12" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2225,7 +2216,7 @@
         <v/>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.12963758773814638</v>
       </c>
       <c r="P13" s="12" t="str">
@@ -2241,7 +2232,7 @@
         <v/>
       </c>
       <c r="S13" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2309,7 +2300,7 @@
         <v/>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.9575596816976457E-3</v>
       </c>
       <c r="P14" s="12" t="str">
@@ -2325,7 +2316,7 @@
         <v/>
       </c>
       <c r="S14" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -2395,7 +2386,7 @@
         <v>23481.15</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.13362013612430967</v>
       </c>
       <c r="P15" s="12">
@@ -2411,7 +2402,7 @@
         <v>0.13362013612430967</v>
       </c>
       <c r="S15" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>3.2782240323238281E-2</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -2447,10 +2438,10 @@
         <v>93</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
@@ -2479,7 +2470,7 @@
         <v/>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2083549110997183E-3</v>
       </c>
       <c r="P16" s="12" t="str">
@@ -2495,7 +2486,7 @@
         <v/>
       </c>
       <c r="S16" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W16=TRUE,IFERROR(N16/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -2565,7 +2556,7 @@
         <v/>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.2594322205086854E-2</v>
       </c>
       <c r="P17" s="12" t="str">
@@ -2581,7 +2572,7 @@
         <v/>
       </c>
       <c r="S17" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -2665,7 +2656,7 @@
         <v/>
       </c>
       <c r="S18" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -2698,13 +2689,13 @@
         <v>92</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
@@ -2724,7 +2715,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-8.1607030759573984E-3</v>
       </c>
       <c r="P19" s="12"/>
@@ -2732,7 +2723,7 @@
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
       <c r="T19" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>35</v>
@@ -2796,7 +2787,7 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.12429378531073432</v>
       </c>
       <c r="P20" s="12" t="str">
@@ -2812,7 +2803,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ref="S20:S32" ca="1" si="12">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$503,$W$2:$W$503,TRUE),0),0)</f>
+        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2880,7 +2871,7 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="P21" s="12" t="str">
@@ -2896,7 +2887,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2923,33 +2914,33 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
-        <v>9</v>
+        <v>262</v>
       </c>
       <c r="H22" s="8">
-        <v>108.73</v>
+        <v>8.89</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2964,8 +2955,8 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.4305159569576027E-2</v>
+        <f t="shared" si="5"/>
+        <v>-0.1001124859392577</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2980,11 +2971,11 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>35</v>
@@ -3007,33 +2998,33 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7">
-        <v>262</v>
+        <v>44</v>
       </c>
       <c r="H23" s="8">
-        <v>8.89</v>
+        <v>56.9</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3048,8 +3039,8 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.1001124859392577</v>
+        <f t="shared" si="5"/>
+        <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3064,11 +3055,11 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>35</v>
@@ -3091,33 +3082,33 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H24" s="8">
-        <v>56.9</v>
+        <v>28.1</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3132,8 +3123,8 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.5817223198594021E-2</v>
+        <f t="shared" si="5"/>
+        <v>-7.4733096085409345E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3148,11 +3139,11 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>35</v>
@@ -3175,33 +3166,33 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="H25" s="8">
-        <v>28.1</v>
+        <v>16.59</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3216,8 +3207,8 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.4733096085409345E-2</v>
+        <f t="shared" si="5"/>
+        <v>-0.27667269439421338</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3232,11 +3223,11 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>35</v>
@@ -3259,33 +3250,33 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="H26" s="8">
-        <v>16.59</v>
+        <v>58.1</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3300,8 +3291,8 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.27667269439421338</v>
+        <f t="shared" si="5"/>
+        <v>-7.056798623063687E-2</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3316,7 +3307,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3343,33 +3334,33 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H27" s="8">
-        <v>58.1</v>
+        <v>95.08</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3384,8 +3375,8 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.056798623063687E-2</v>
+        <f t="shared" si="5"/>
+        <v>-0.2111905763567522</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3400,11 +3391,11 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>35</v>
@@ -3427,33 +3418,33 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H28" s="8">
-        <v>95.08</v>
+        <v>77.56</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3468,8 +3459,8 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.2111905763567522</v>
+        <f t="shared" si="5"/>
+        <v>5.6730273336771386E-3</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3484,11 +3475,11 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="U28" s="6" t="s">
         <v>35</v>
@@ -3511,33 +3502,33 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H29" s="8">
-        <v>77.56</v>
+        <v>166.35</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="8">
-        <v>78</v>
+        <v>175.52</v>
       </c>
       <c r="L29" s="13" t="str">
         <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3552,8 +3543,8 @@
         <v/>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
-        <v>5.6730273336771386E-3</v>
+        <f t="shared" si="5"/>
+        <v>5.5124737000300739E-2</v>
       </c>
       <c r="P29" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3568,14 +3559,14 @@
         <v/>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="V29" s="10" t="b">
         <v>1</v>
@@ -3595,71 +3586,56 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H30" s="8">
-        <v>166.35</v>
+        <v>80.75</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="8">
-        <v>175.52</v>
-      </c>
-      <c r="L30" s="13" t="str">
-        <f ca="1">IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
+        <v>80.75</v>
+      </c>
+      <c r="L30" s="13"/>
       <c r="M30" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N30" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+      <c r="N30" s="11"/>
       <c r="O30" s="12">
-        <f t="shared" si="6"/>
-        <v>5.5124737000300739E-2</v>
-      </c>
-      <c r="P30" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q30" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R30" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="12"/>
       <c r="S30" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W30=TRUE,IFERROR(N30/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="V30" s="10" t="b">
         <v>1</v>
@@ -3679,59 +3655,77 @@
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7">
-        <v>17</v>
+        <f>260</f>
+        <v>260</v>
       </c>
       <c r="H31" s="8">
-        <v>80.75</v>
+        <v>637</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J31" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J31" s="9">
+        <v>1</v>
+      </c>
       <c r="K31" s="8">
-        <v>80.75</v>
-      </c>
-      <c r="L31" s="13"/>
+        <v>1662</v>
+      </c>
+      <c r="L31" s="13">
+        <f>IF(I31="DKK",1,IFERROR(_xludf.XLOOKUP(I31,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="11"/>
+        <v>165620</v>
+      </c>
+      <c r="N31" s="11">
+        <f>IFERROR(G31*K31*L31,"")</f>
+        <v>432120</v>
+      </c>
       <c r="O31" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="12"/>
+        <f t="shared" si="5"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="P31" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="11">
+        <f t="shared" si="3"/>
+        <v>266500</v>
+      </c>
+      <c r="R31" s="12">
+        <f t="shared" si="4"/>
+        <v>1.609105180533752</v>
+      </c>
       <c r="S31" s="12">
-        <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <f ca="1">IF(W31=TRUE,IFERROR(N31/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <v>0.60328653786027198</v>
       </c>
       <c r="T31" s="6" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="U31" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="V31" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="10" t="b">
         <v>1</v>
@@ -3746,97 +3740,10 @@
       <c r="AA31" s="14"/>
       <c r="AB31" s="14"/>
     </row>
-    <row r="32" spans="1:28">
-      <c r="A32" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="H32" s="8">
-        <v>637</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="9">
-        <v>1</v>
-      </c>
-      <c r="K32" s="8">
-        <v>1662</v>
-      </c>
-      <c r="L32" s="13">
-        <f>IF(I32="DKK",1,IFERROR(_xludf.XLOOKUP(I32,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
-      </c>
-      <c r="M32" s="11">
-        <f t="shared" si="0"/>
-        <v>165620</v>
-      </c>
-      <c r="N32" s="11">
-        <f>IFERROR(G32*K32*L32,"")</f>
-        <v>432120</v>
-      </c>
-      <c r="O32" s="12">
-        <f t="shared" si="6"/>
-        <v>1.609105180533752</v>
-      </c>
-      <c r="P32" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11">
-        <f t="shared" si="3"/>
-        <v>266500</v>
-      </c>
-      <c r="R32" s="12">
-        <f t="shared" si="4"/>
-        <v>1.609105180533752</v>
-      </c>
-      <c r="S32" s="12">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.60328653786027198</v>
-      </c>
-      <c r="T32" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="U32" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="V32" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="W32" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="X32" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="14"/>
-      <c r="AB32" s="14"/>
-    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:S32">
+  <conditionalFormatting sqref="G2:S31">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3867,16 +3774,16 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>27</v>
@@ -3887,7 +3794,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3901,13 +3808,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>1</v>
@@ -3918,22 +3825,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>148</v>
-      </c>
-      <c r="C4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3958,150 +3865,150 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" t="s">
         <v>155</v>
-      </c>
-      <c r="B2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B3" s="5">
         <v>0.02</v>
       </c>
       <c r="C3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B4" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B5" s="5">
         <v>0.25</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B6" s="5">
         <v>0.25</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B7" s="5">
         <v>0.2</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B8" s="5">
         <v>0.2</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B9" s="5">
         <v>0.1</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" t="s">
         <v>169</v>
-      </c>
-      <c r="B10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -4140,19 +4047,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4163,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4172,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4181,13 +4088,13 @@
       </c>
       <c r="B3" s="3"/>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4196,13 +4103,13 @@
       </c>
       <c r="B4" s="3"/>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4211,73 +4118,73 @@
       </c>
       <c r="B5" s="3"/>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B6" s="3"/>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4298,7 +4205,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -4317,16 +4224,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4337,16 +4244,16 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4357,16 +4264,16 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4377,36 +4284,36 @@
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4417,16 +4324,16 @@
         <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4440,10 +4347,10 @@
         <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4454,16 +4361,16 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4477,10 +4384,10 @@
         <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4494,10 +4401,10 @@
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4508,36 +4415,36 @@
         <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D11" t="s">
         <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4548,16 +4455,16 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4568,16 +4475,16 @@
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D14" t="s">
         <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4588,16 +4495,16 @@
         <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F15" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4608,36 +4515,36 @@
         <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s">
         <v>42</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4651,27 +4558,27 @@
         <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F18" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4685,10 +4592,10 @@
         <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4702,10 +4609,10 @@
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4719,197 +4626,180 @@
         <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F22" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F25" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F27" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F28" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F29" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F32" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>141</v>
-      </c>
-      <c r="B33" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4954,16 +4844,16 @@
         <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>27</v>
@@ -4971,13 +4861,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2" t="s">
         <v>212</v>
-      </c>
-      <c r="B2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" t="s">
-        <v>214</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -4989,7 +4879,7 @@
         <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -5028,19 +4918,19 @@
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5051,14 +4941,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>66709</v>
+        <v>74388</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>66709</v>
+        <v>74388</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994C77B5-3B73-435D-BB07-1C1148A6F164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF36EE0-1E8A-4024-82BB-A8C598DCFDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1316,7 +1316,7 @@
         <v/>
       </c>
       <c r="S2" s="12">
-        <f ca="1">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S18" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1386,7 +1386,7 @@
         <v>40800</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O31" si="5">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
         <v>0.29302476522726817</v>
       </c>
       <c r="P3" s="12">
@@ -1402,7 +1402,7 @@
         <v>0.29302476522726817</v>
       </c>
       <c r="S3" s="12">
-        <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>5.6961239342541645E-2</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1470,7 +1470,7 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.38622291738007752</v>
       </c>
       <c r="P4" s="12" t="str">
@@ -1486,7 +1486,7 @@
         <v/>
       </c>
       <c r="S4" s="12">
-        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1545,23 +1545,23 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="12">
-        <f t="shared" ref="O5" si="6">IFERROR(K5/H5-1,"")</f>
+        <f t="shared" ref="O5" si="7">IFERROR(K5/H5-1,"")</f>
         <v>-2.3346057986560753E-3</v>
       </c>
       <c r="P5" s="12" t="str">
-        <f t="shared" ref="P5" si="7">IFERROR(L5/J5-1,"")</f>
+        <f t="shared" ref="P5" si="8">IFERROR(L5/J5-1,"")</f>
         <v/>
       </c>
       <c r="Q5" s="11">
-        <f t="shared" ref="Q5" si="8">IFERROR(N5-M5,"")</f>
+        <f t="shared" ref="Q5" si="9">IFERROR(N5-M5,"")</f>
         <v>0</v>
       </c>
       <c r="R5" s="12" t="str">
-        <f t="shared" ref="R5" si="9">IFERROR(N5/M5-1,"")</f>
+        <f t="shared" ref="R5" si="10">IFERROR(N5/M5-1,"")</f>
         <v/>
       </c>
       <c r="S5" s="12">
-        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1631,7 +1631,7 @@
         <v>47175</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.77893000235682286</v>
       </c>
       <c r="P6" s="12">
@@ -1647,7 +1647,7 @@
         <v>0.77893000235682308</v>
       </c>
       <c r="S6" s="12">
-        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>6.586143298981377E-2</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1715,7 +1715,7 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.1202990983065757</v>
       </c>
       <c r="P7" s="12" t="str">
@@ -1731,7 +1731,7 @@
         <v/>
       </c>
       <c r="S7" s="12">
-        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.6576234262988541E-2</v>
       </c>
       <c r="P8" s="12" t="str">
@@ -1815,7 +1815,7 @@
         <v/>
       </c>
       <c r="S8" s="12">
-        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1885,7 +1885,7 @@
         <v>57330</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2431473082232301</v>
       </c>
       <c r="P9" s="12">
@@ -1901,7 +1901,7 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S9" s="12">
-        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>8.0038917929115508E-2</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1971,7 +1971,7 @@
         <v>100128</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.32731376975169302</v>
       </c>
       <c r="P10" s="12">
@@ -1987,7 +1987,7 @@
         <v>-0.32731376975169302</v>
       </c>
       <c r="S10" s="12">
-        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0.13978958266887279</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -2057,7 +2057,7 @@
         <v>15242.4</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.41251042535446203</v>
       </c>
       <c r="P11" s="12">
@@ -2073,7 +2073,7 @@
         <v>0.41251042535446203</v>
       </c>
       <c r="S11" s="12">
-        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>2.1280048886146E-2</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2148,7 +2148,7 @@
         <v/>
       </c>
       <c r="S12" s="12">
-        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2216,7 +2216,7 @@
         <v/>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.12963758773814638</v>
       </c>
       <c r="P13" s="12" t="str">
@@ -2232,7 +2232,7 @@
         <v/>
       </c>
       <c r="S13" s="12">
-        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2300,7 +2300,7 @@
         <v/>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.9575596816976457E-3</v>
       </c>
       <c r="P14" s="12" t="str">
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="S14" s="12">
-        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -2386,7 +2386,7 @@
         <v>23481.15</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.13362013612430967</v>
       </c>
       <c r="P15" s="12">
@@ -2402,7 +2402,7 @@
         <v>0.13362013612430967</v>
       </c>
       <c r="S15" s="12">
-        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>3.2782240323238281E-2</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2083549110997183E-3</v>
       </c>
       <c r="P16" s="12" t="str">
@@ -2486,7 +2486,7 @@
         <v/>
       </c>
       <c r="S16" s="12">
-        <f ca="1">IF(W16=TRUE,IFERROR(N16/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -2556,7 +2556,7 @@
         <v/>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.2594322205086854E-2</v>
       </c>
       <c r="P17" s="12" t="str">
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="S17" s="12">
-        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -2656,7 +2656,7 @@
         <v/>
       </c>
       <c r="S18" s="12">
-        <f ca="1">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -2699,10 +2699,10 @@
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H19" s="8">
-        <v>79.650000000000006</v>
+        <v>80.14</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
@@ -2715,8 +2715,8 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="12">
-        <f t="shared" si="5"/>
-        <v>-8.1607030759573984E-3</v>
+        <f t="shared" si="6"/>
+        <v>-1.4225106064387316E-2</v>
       </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="11"/>
@@ -2787,7 +2787,7 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.12429378531073432</v>
       </c>
       <c r="P20" s="12" t="str">
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ref="S20:S31" ca="1" si="11">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2871,7 +2871,7 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.7</v>
       </c>
       <c r="P21" s="12" t="str">
@@ -2887,7 +2887,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2955,7 +2955,7 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.1001124859392577</v>
       </c>
       <c r="P22" s="12" t="str">
@@ -2971,7 +2971,7 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -3039,7 +3039,7 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P23" s="12" t="str">
@@ -3055,7 +3055,7 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -3123,7 +3123,7 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.4733096085409345E-2</v>
       </c>
       <c r="P24" s="12" t="str">
@@ -3139,7 +3139,7 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3207,7 +3207,7 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.27667269439421338</v>
       </c>
       <c r="P25" s="12" t="str">
@@ -3223,7 +3223,7 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3291,7 +3291,7 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.056798623063687E-2</v>
       </c>
       <c r="P26" s="12" t="str">
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3375,7 +3375,7 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.2111905763567522</v>
       </c>
       <c r="P27" s="12" t="str">
@@ -3391,7 +3391,7 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.6730273336771386E-3</v>
       </c>
       <c r="P28" s="12" t="str">
@@ -3475,7 +3475,7 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -3543,7 +3543,7 @@
         <v/>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.5124737000300739E-2</v>
       </c>
       <c r="P29" s="12" t="str">
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="S29" s="12">
-        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -3621,14 +3621,14 @@
       </c>
       <c r="N30" s="11"/>
       <c r="O30" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P30" s="12"/>
       <c r="Q30" s="11"/>
       <c r="R30" s="12"/>
       <c r="S30" s="12">
-        <f ca="1">IF(W30=TRUE,IFERROR(N30/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -3699,7 +3699,7 @@
         <v>432120</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.609105180533752</v>
       </c>
       <c r="P31" s="12">
@@ -3715,7 +3715,7 @@
         <v>1.609105180533752</v>
       </c>
       <c r="S31" s="12">
-        <f ca="1">IF(W31=TRUE,IFERROR(N31/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0.60328653786027198</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -4941,14 +4941,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>74388</v>
+        <v>65251</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>74388</v>
+        <v>65251</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF36EE0-1E8A-4024-82BB-A8C598DCFDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF51D45-9659-49F4-8ECA-B5E9B781814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.6961239342541645E-2</v>
+        <v>5.6626512963620028E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>6.586143298981377E-2</v>
+        <v>6.547440561418566E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>8.0038917929115508E-2</v>
+        <v>7.9568578142263147E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13978958266887279</v>
+        <v>0.13896812475542517</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2030,10 +2030,10 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H11" s="8">
-        <v>599.5</v>
+        <v>649.4</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>42</v>
@@ -2050,15 +2050,15 @@
       </c>
       <c r="M11" s="11">
         <f t="shared" si="0"/>
-        <v>10791</v>
+        <v>14936.199999999999</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>15242.4</v>
+        <v>19476.399999999998</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
-        <v>0.41251042535446203</v>
+        <v>0.30397289805974737</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="2"/>
@@ -2066,15 +2066,15 @@
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>4451.3999999999996</v>
+        <v>4540.1999999999989</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="4"/>
-        <v>0.41251042535446203</v>
+        <v>0.30397289805974737</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1280048886146E-2</v>
+        <v>2.7031387673643357E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2782240323238281E-2</v>
+        <v>3.2589599139110456E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>0.60328653786027198</v>
+        <v>0.59974139171175211</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>
@@ -4941,14 +4941,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>65251</v>
+        <v>61074</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>65251</v>
+        <v>61074</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF51D45-9659-49F4-8ECA-B5E9B781814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F7E2E6-C4B7-4637-B2A7-4D38E516E6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.6626512963620028E-2</v>
+        <v>4.0182833863827171E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>6.547440561418566E-2</v>
+        <v>4.6461401655050166E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.9568578142263147E-2</v>
+        <v>5.6462790818951267E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7">
-        <v>336</v>
+        <v>436</v>
       </c>
       <c r="H10" s="8">
         <v>443</v>
@@ -1964,11 +1964,11 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="0"/>
-        <v>148848</v>
+        <v>193148</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>100128</v>
+        <v>129928</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>-48720</v>
+        <v>-63220</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13896812475542517</v>
+        <v>0.12796262838870923</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="H11" s="8">
         <v>649.4</v>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="M11" s="11">
         <f t="shared" si="0"/>
-        <v>14936.199999999999</v>
+        <v>218198.39999999999</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>19476.399999999998</v>
+        <v>284524.79999999999</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>4540.1999999999989</v>
+        <v>66326.399999999994</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="4"/>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.7031387673643357E-2</v>
+        <v>0.28022090118967286</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2589599139110456E-2</v>
+        <v>2.3125959543666797E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="U30" s="6" t="s">
         <v>137</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>0.59974139171175211</v>
+        <v>0.42558348454012246</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F7E2E6-C4B7-4637-B2A7-4D38E516E6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA829CA7-150E-4B73-9C7F-26E616C0844B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.0182833863827171E-2</v>
+        <v>5.4377484096418474E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.6461401655050166E-2</v>
+        <v>6.2873965986483857E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.6462790818951267E-2</v>
+        <v>7.6408361844305661E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.12796262838870923</v>
+        <v>0.17316563121763381</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>336</v>
+        <v>23</v>
       </c>
       <c r="H11" s="8">
         <v>649.4</v>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="M11" s="11">
         <f t="shared" si="0"/>
-        <v>218198.39999999999</v>
+        <v>14936.199999999999</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>284524.79999999999</v>
+        <v>19476.399999999998</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>66326.399999999994</v>
+        <v>4540.1999999999989</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="4"/>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.28022090118967286</v>
+        <v>2.5957785079791289E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.3125959543666797E-2</v>
+        <v>3.1295241683593544E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>0.42558348454012246</v>
+        <v>0.57592153009177327</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA829CA7-150E-4B73-9C7F-26E616C0844B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EC8002-8CC3-43AD-BDE3-3471B0DC01DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.4377484096418474E-2</v>
+        <v>5.4628818268198175E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>6.2873965986483857E-2</v>
+        <v>6.3164571122604138E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.6408361844305661E-2</v>
+        <v>7.6761523316563759E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1944,10 +1944,10 @@
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7">
-        <v>436</v>
+        <v>396</v>
       </c>
       <c r="H10" s="8">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>42</v>
@@ -1964,15 +1964,15 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="0"/>
-        <v>193148</v>
+        <v>171468</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>129928</v>
+        <v>118008</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>-0.32731376975169302</v>
+        <v>-0.31177829099307164</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1980,15 +1980,15 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>-63220</v>
+        <v>-53460</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>-0.32731376975169302</v>
+        <v>-0.31177829099307164</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.17316563121763381</v>
+        <v>0.15800582319101789</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2030,10 +2030,10 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H11" s="8">
-        <v>649.4</v>
+        <v>710.62</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>42</v>
@@ -2050,15 +2050,15 @@
       </c>
       <c r="M11" s="11">
         <f t="shared" si="0"/>
-        <v>14936.199999999999</v>
+        <v>23450.46</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>19476.399999999998</v>
+        <v>27944.399999999998</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
-        <v>0.30397289805974737</v>
+        <v>0.19163547324871222</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="2"/>
@@ -2066,15 +2066,15 @@
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>4540.1999999999989</v>
+        <v>4493.9399999999987</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="4"/>
-        <v>0.30397289805974737</v>
+        <v>0.19163547324871244</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.5957785079791289E-2</v>
+        <v>3.7415920323868548E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.1295241683593544E-2</v>
+        <v>3.1439889119566217E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>0.57592153009177327</v>
+        <v>0.57858345465818117</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>
@@ -4941,14 +4941,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>61074</v>
+        <v>65831</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>61074</v>
+        <v>65831</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EC8002-8CC3-43AD-BDE3-3471B0DC01DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E513E6-75CB-46A1-A1B2-CC63F44F5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1690,10 +1690,10 @@
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H7" s="8">
-        <v>45.47</v>
+        <v>47.25</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>57</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1202990983065757</v>
+        <v>-0.15343915343915349</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E513E6-75CB-46A1-A1B2-CC63F44F5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9091B68B-1277-4369-8417-7364C731848F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1275,10 +1275,10 @@
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="7">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H2" s="8">
-        <v>858.39</v>
+        <v>923.49</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>33</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>0.13468237048427878</v>
+        <v>5.4694690792536971E-2</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9091B68B-1277-4369-8417-7364C731848F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45142E2D-6F0C-4865-BC9B-AC0DD38F3C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1445,10 +1445,10 @@
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="8">
-        <v>1080.49</v>
+        <v>1126.28</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>48</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>0.38622291738007752</v>
+        <v>0.32986468728912888</v>
       </c>
       <c r="P4" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2275,10 +2275,10 @@
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H14" s="8">
-        <v>414.7</v>
+        <v>408.97</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>57</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>7.9575596816976457E-3</v>
+        <v>2.2079859158373516E-2</v>
       </c>
       <c r="P14" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2445,10 +2445,10 @@
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H16" s="8">
-        <v>57.93</v>
+        <v>60.59</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>57</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>1.2083549110997183E-3</v>
+        <v>-4.2746327776860937E-2</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2846,10 +2846,10 @@
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
-        <v>363</v>
+        <v>313</v>
       </c>
       <c r="H21" s="8">
-        <v>10</v>
+        <v>10.427</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>48</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="O21" s="12">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.63038266040088242</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4941,14 +4941,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>65831</v>
+        <v>126504</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>65831</v>
+        <v>126504</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45142E2D-6F0C-4865-BC9B-AC0DD38F3C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A231C32-509A-4B57-876E-24096AF81E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>5.4628818268198175E-2</v>
+        <v>5.5005901000702934E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>6.3164571122604138E-2</v>
+        <v>6.3600573032062777E-2</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>43</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.6761523316563759E-2</v>
+        <v>7.7291380009075969E-2</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>58</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.15800582319101789</v>
+        <v>0.1590964795414449</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>69</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.7415920323868548E-2</v>
+        <v>3.7674188723628502E-2</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>74</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="H15" s="8">
         <v>155.74</v>
@@ -2379,11 +2379,11 @@
       </c>
       <c r="M15" s="11">
         <f>IFERROR(G15*H15*J15,"")</f>
-        <v>20713.420000000002</v>
+        <v>16196.960000000001</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>23481.15</v>
+        <v>18361.2</v>
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="3"/>
-        <v>2767.7299999999996</v>
+        <v>2164.2399999999998</v>
       </c>
       <c r="R15" s="12">
         <f t="shared" si="4"/>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.1439889119566217E-2</v>
+        <v>2.4754273270933991E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>90</v>
@@ -3098,10 +3098,10 @@
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H24" s="8">
-        <v>28.1</v>
+        <v>27.024999999999999</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4733096085409345E-2</v>
+        <v>-3.7927844588344084E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="S31" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>0.57858345465818117</v>
+        <v>0.58257720442215077</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>58</v>
@@ -4941,14 +4941,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>126504</v>
+        <v>136930</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>126504</v>
+        <v>136930</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A231C32-509A-4B57-876E-24096AF81E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1551BE9-5C93-45A6-890E-C3E835FF4314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H12" s="8">
-        <v>110.64</v>
+        <v>123.66</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>48</v>
@@ -2133,7 +2133,7 @@
       <c r="N12" s="11"/>
       <c r="O12" s="12">
         <f>IFERROR(K12/H12-1,"")</f>
-        <v>1.4461315979754641E-3</v>
+        <v>-0.10399482451884201</v>
       </c>
       <c r="P12" s="12" t="str">
         <f>IFERROR(L12/J12-1,"")</f>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1551BE9-5C93-45A6-890E-C3E835FF4314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854CFE81-4562-41E0-99E8-192F7AA1137D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="216">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -434,12 +434,6 @@
     <t>A026</t>
   </si>
   <si>
-    <t>Xtrackers MSCI World Industrials UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>XDWI.DE</t>
-  </si>
-  <si>
     <t>A027</t>
   </si>
   <si>
@@ -654,9 +648,6 @@
   </si>
   <si>
     <t>IS3Q.DE</t>
-  </si>
-  <si>
-    <t>A029</t>
   </si>
   <si>
     <t>ServiceNow Inc</t>
@@ -863,7 +854,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB30">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Asset_Type"/>
@@ -940,7 +931,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F31">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Yahoo_Ticker"/>
@@ -1138,7 +1129,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1292,11 +1283,11 @@
         <v/>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M31" si="0">IFERROR(G2*H2*J2,"")</f>
+        <f t="shared" ref="M2:M30" si="0">IFERROR(G2*H2*J2,"")</f>
         <v>0</v>
       </c>
       <c r="N2" s="11" t="str">
-        <f t="shared" ref="N2:N29" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
+        <f t="shared" ref="N2:N28" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
         <v/>
       </c>
       <c r="O2" s="12">
@@ -1304,19 +1295,19 @@
         <v>5.4694690792536971E-2</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P31" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P30" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q31" ca="1" si="3">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q30" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R31" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R30" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S18" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f ca="1">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1386,7 +1377,7 @@
         <v>40800</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O31" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O30" si="5">IFERROR(K3/H3-1,"")</f>
         <v>0.29302476522726817</v>
       </c>
       <c r="P3" s="12">
@@ -1402,7 +1393,7 @@
         <v>0.29302476522726817</v>
       </c>
       <c r="S3" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>5.5005901000702934E-2</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1470,7 +1461,7 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.32986468728912888</v>
       </c>
       <c r="P4" s="12" t="str">
@@ -1486,7 +1477,7 @@
         <v/>
       </c>
       <c r="S4" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1519,13 +1510,13 @@
         <v>29</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7">
@@ -1545,23 +1536,23 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="12">
-        <f t="shared" ref="O5" si="7">IFERROR(K5/H5-1,"")</f>
+        <f t="shared" ref="O5" si="6">IFERROR(K5/H5-1,"")</f>
         <v>-2.3346057986560753E-3</v>
       </c>
       <c r="P5" s="12" t="str">
-        <f t="shared" ref="P5" si="8">IFERROR(L5/J5-1,"")</f>
+        <f t="shared" ref="P5" si="7">IFERROR(L5/J5-1,"")</f>
         <v/>
       </c>
       <c r="Q5" s="11">
-        <f t="shared" ref="Q5" si="9">IFERROR(N5-M5,"")</f>
+        <f t="shared" ref="Q5" si="8">IFERROR(N5-M5,"")</f>
         <v>0</v>
       </c>
       <c r="R5" s="12" t="str">
-        <f t="shared" ref="R5" si="10">IFERROR(N5/M5-1,"")</f>
+        <f t="shared" ref="R5" si="9">IFERROR(N5/M5-1,"")</f>
         <v/>
       </c>
       <c r="S5" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1631,7 +1622,7 @@
         <v>47175</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.77893000235682286</v>
       </c>
       <c r="P6" s="12">
@@ -1647,7 +1638,7 @@
         <v>0.77893000235682308</v>
       </c>
       <c r="S6" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>6.3600573032062777E-2</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1715,7 +1706,7 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.15343915343915349</v>
       </c>
       <c r="P7" s="12" t="str">
@@ -1731,7 +1722,7 @@
         <v/>
       </c>
       <c r="S7" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1799,7 +1790,7 @@
         <v/>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.6576234262988541E-2</v>
       </c>
       <c r="P8" s="12" t="str">
@@ -1815,7 +1806,7 @@
         <v/>
       </c>
       <c r="S8" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1885,7 +1876,7 @@
         <v>57330</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2431473082232301</v>
       </c>
       <c r="P9" s="12">
@@ -1901,7 +1892,7 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>7.7291380009075969E-2</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1971,7 +1962,7 @@
         <v>118008</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.31177829099307164</v>
       </c>
       <c r="P10" s="12">
@@ -1987,7 +1978,7 @@
         <v>-0.31177829099307164</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0.1590964795414449</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -2057,7 +2048,7 @@
         <v>27944.399999999998</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.19163547324871222</v>
       </c>
       <c r="P11" s="12">
@@ -2073,7 +2064,7 @@
         <v>0.19163547324871244</v>
       </c>
       <c r="S11" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>3.7674188723628502E-2</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2106,13 +2097,13 @@
         <v>29</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
@@ -2148,7 +2139,7 @@
         <v/>
       </c>
       <c r="S12" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2216,7 +2207,7 @@
         <v/>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.12963758773814638</v>
       </c>
       <c r="P13" s="12" t="str">
@@ -2232,7 +2223,7 @@
         <v/>
       </c>
       <c r="S13" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2300,7 +2291,7 @@
         <v/>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.2079859158373516E-2</v>
       </c>
       <c r="P14" s="12" t="str">
@@ -2316,7 +2307,7 @@
         <v/>
       </c>
       <c r="S14" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -2386,7 +2377,7 @@
         <v>18361.2</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.13362013612430967</v>
       </c>
       <c r="P15" s="12">
@@ -2402,7 +2393,7 @@
         <v>0.13362013612430967</v>
       </c>
       <c r="S15" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>2.4754273270933991E-2</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -2438,10 +2429,10 @@
         <v>93</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
@@ -2470,7 +2461,7 @@
         <v/>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-4.2746327776860937E-2</v>
       </c>
       <c r="P16" s="12" t="str">
@@ -2486,7 +2477,7 @@
         <v/>
       </c>
       <c r="S16" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W16=TRUE,IFERROR(N16/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -2556,7 +2547,7 @@
         <v/>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.2594322205086854E-2</v>
       </c>
       <c r="P17" s="12" t="str">
@@ -2572,7 +2563,7 @@
         <v/>
       </c>
       <c r="S17" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -2656,7 +2647,7 @@
         <v/>
       </c>
       <c r="S18" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -2689,13 +2680,13 @@
         <v>92</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
@@ -2715,7 +2706,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-1.4225106064387316E-2</v>
       </c>
       <c r="P19" s="12"/>
@@ -2723,7 +2714,7 @@
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
       <c r="T19" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>35</v>
@@ -2787,7 +2778,7 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.12429378531073432</v>
       </c>
       <c r="P20" s="12" t="str">
@@ -2803,7 +2794,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ref="S20:S31" ca="1" si="11">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$502,$W$2:$W$502,TRUE),0),0)</f>
+        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2871,7 +2862,7 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.63038266040088242</v>
       </c>
       <c r="P21" s="12" t="str">
@@ -2887,7 +2878,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2955,7 +2946,7 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.1001124859392577</v>
       </c>
       <c r="P22" s="12" t="str">
@@ -2971,7 +2962,7 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -3039,7 +3030,7 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P23" s="12" t="str">
@@ -3055,7 +3046,7 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -3123,7 +3114,7 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-3.7927844588344084E-2</v>
       </c>
       <c r="P24" s="12" t="str">
@@ -3139,7 +3130,7 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3207,7 +3198,7 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.27667269439421338</v>
       </c>
       <c r="P25" s="12" t="str">
@@ -3223,7 +3214,7 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3291,7 +3282,7 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-7.056798623063687E-2</v>
       </c>
       <c r="P26" s="12" t="str">
@@ -3307,7 +3298,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3375,7 +3366,7 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.2111905763567522</v>
       </c>
       <c r="P27" s="12" t="str">
@@ -3391,7 +3382,7 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -3424,27 +3415,27 @@
         <v>92</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H28" s="8">
-        <v>77.56</v>
+        <v>166.35</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>78</v>
+        <v>175.52</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3459,8 +3450,8 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
-        <v>5.6730273336771386E-3</v>
+        <f t="shared" si="5"/>
+        <v>5.5124737000300739E-2</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3475,14 +3466,14 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="V28" s="10" t="b">
         <v>1</v>
@@ -3502,71 +3493,56 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H29" s="8">
-        <v>166.35</v>
+        <v>80.75</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="8">
-        <v>175.52</v>
-      </c>
-      <c r="L29" s="13" t="str">
-        <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
+        <v>80.75</v>
+      </c>
+      <c r="L29" s="13"/>
       <c r="M29" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N29" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+      <c r="N29" s="11"/>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
-        <v>5.5124737000300739E-2</v>
-      </c>
-      <c r="P29" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q29" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R29" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="12"/>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="V29" s="10" t="b">
         <v>1</v>
@@ -3586,59 +3562,77 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7">
-        <v>17</v>
+        <f>260</f>
+        <v>260</v>
       </c>
       <c r="H30" s="8">
-        <v>80.75</v>
+        <v>637</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J30" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J30" s="9">
+        <v>1</v>
+      </c>
       <c r="K30" s="8">
-        <v>80.75</v>
-      </c>
-      <c r="L30" s="13"/>
+        <v>1662</v>
+      </c>
+      <c r="L30" s="13">
+        <f>IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
       <c r="M30" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="11"/>
+        <v>165620</v>
+      </c>
+      <c r="N30" s="11">
+        <f>IFERROR(G30*K30*L30,"")</f>
+        <v>432120</v>
+      </c>
       <c r="O30" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="12"/>
+        <f t="shared" si="5"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="P30" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="11">
+        <f t="shared" si="3"/>
+        <v>266500</v>
+      </c>
+      <c r="R30" s="12">
+        <f t="shared" si="4"/>
+        <v>1.609105180533752</v>
+      </c>
       <c r="S30" s="12">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <f ca="1">IF(W30=TRUE,IFERROR(N30/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>0.58257720442215077</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="V30" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" s="10" t="b">
         <v>1</v>
@@ -3653,97 +3647,10 @@
       <c r="AA30" s="14"/>
       <c r="AB30" s="14"/>
     </row>
-    <row r="31" spans="1:28">
-      <c r="A31" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="H31" s="8">
-        <v>637</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" s="9">
-        <v>1</v>
-      </c>
-      <c r="K31" s="8">
-        <v>1662</v>
-      </c>
-      <c r="L31" s="13">
-        <f>IF(I31="DKK",1,IFERROR(_xludf.XLOOKUP(I31,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
-      </c>
-      <c r="M31" s="11">
-        <f t="shared" si="0"/>
-        <v>165620</v>
-      </c>
-      <c r="N31" s="11">
-        <f>IFERROR(G31*K31*L31,"")</f>
-        <v>432120</v>
-      </c>
-      <c r="O31" s="12">
-        <f t="shared" si="6"/>
-        <v>1.609105180533752</v>
-      </c>
-      <c r="P31" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="11">
-        <f t="shared" si="3"/>
-        <v>266500</v>
-      </c>
-      <c r="R31" s="12">
-        <f t="shared" si="4"/>
-        <v>1.609105180533752</v>
-      </c>
-      <c r="S31" s="12">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.58257720442215077</v>
-      </c>
-      <c r="T31" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="U31" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="V31" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="W31" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="X31" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:S31">
+  <conditionalFormatting sqref="G2:S30">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3774,16 +3681,16 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>27</v>
@@ -3794,7 +3701,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3808,13 +3715,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>1</v>
@@ -3825,22 +3732,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>146</v>
-      </c>
-      <c r="C4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3865,150 +3772,150 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
         <v>153</v>
-      </c>
-      <c r="B2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B3" s="5">
         <v>0.02</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B4" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B5" s="5">
         <v>0.25</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B6" s="5">
         <v>0.25</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B7" s="5">
         <v>0.2</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B8" s="5">
         <v>0.2</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B9" s="5">
         <v>0.1</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
         <v>167</v>
-      </c>
-      <c r="B10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D10" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4047,19 +3954,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4070,7 +3977,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4079,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4088,13 +3995,13 @@
       </c>
       <c r="B3" s="3"/>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4103,13 +4010,13 @@
       </c>
       <c r="B4" s="3"/>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4118,73 +4025,73 @@
       </c>
       <c r="B5" s="3"/>
       <c r="D5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B6" s="3"/>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4205,7 +4112,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -4224,16 +4131,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4244,16 +4151,16 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4264,16 +4171,16 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4284,36 +4191,36 @@
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4324,16 +4231,16 @@
         <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4347,10 +4254,10 @@
         <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4361,16 +4268,16 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4384,10 +4291,10 @@
         <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4401,10 +4308,10 @@
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4415,36 +4322,36 @@
         <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
         <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4455,16 +4362,16 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4475,16 +4382,16 @@
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D14" t="s">
         <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4495,16 +4402,16 @@
         <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4515,36 +4422,36 @@
         <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
         <v>42</v>
       </c>
       <c r="E16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4558,27 +4465,27 @@
         <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4592,10 +4499,10 @@
         <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4609,10 +4516,10 @@
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4626,10 +4533,10 @@
         <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4643,10 +4550,10 @@
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4660,10 +4567,10 @@
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4677,10 +4584,10 @@
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F25" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4694,10 +4601,10 @@
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4711,10 +4618,10 @@
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F27" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4728,78 +4635,61 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F28" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F30" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F31" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" t="s">
-        <v>190</v>
-      </c>
-      <c r="F32" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -4844,16 +4734,16 @@
         <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>27</v>
@@ -4861,13 +4751,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -4879,7 +4769,7 @@
         <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -4918,19 +4808,19 @@
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4941,14 +4831,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>136930</v>
+        <v>138602</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>136930</v>
+        <v>138602</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854CFE81-4562-41E0-99E8-192F7AA1137D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6399DF8C-2FAA-40A5-9B5D-77809B45B831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="220">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -290,9 +290,6 @@
     <t>TSM</t>
   </si>
   <si>
-    <t>A012</t>
-  </si>
-  <si>
     <t>UNH:XETR</t>
   </si>
   <si>
@@ -650,9 +647,6 @@
     <t>IS3Q.DE</t>
   </si>
   <si>
-    <t>ServiceNow Inc</t>
-  </si>
-  <si>
     <t>4S0.DE</t>
   </si>
   <si>
@@ -687,6 +681,24 @@
   </si>
   <si>
     <t>VGWD.DE</t>
+  </si>
+  <si>
+    <t>A029</t>
+  </si>
+  <si>
+    <t>A030</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. Class C</t>
+  </si>
+  <si>
+    <t>GOOG:MIL</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>MIL</t>
   </si>
 </sst>
 </file>
@@ -931,7 +943,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F32">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Yahoo_Ticker"/>
@@ -1426,60 +1438,39 @@
         <v>29</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>47</v>
+        <v>217</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="8">
-        <v>1126.28</v>
+        <v>254.9</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="8">
-        <v>1497.8</v>
-      </c>
-      <c r="L4" s="13" t="str">
-        <f ca="1">IF(I4="DKK",1,IFERROR(_xludf.XLOOKUP(I4,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M4" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>253.95</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
       <c r="O4" s="12">
         <f t="shared" si="5"/>
-        <v>0.32986468728912888</v>
-      </c>
-      <c r="P4" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q4" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R4" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S4" s="12">
-        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0</v>
-      </c>
+        <v>-3.7269517457827472E-3</v>
+      </c>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
       <c r="T4" s="6" t="s">
         <v>49</v>
       </c>
@@ -1510,45 +1501,54 @@
         <v>29</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>212</v>
+        <v>46</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="8">
-        <v>316.97000000000003</v>
+        <v>1199.3</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="8">
-        <v>316.23</v>
-      </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
+        <v>1497.8</v>
+      </c>
+      <c r="L5" s="13" t="str">
+        <f ca="1">IF(I5="DKK",1,IFERROR(_xludf.XLOOKUP(I5,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
+      </c>
+      <c r="M5" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="O5" s="12">
-        <f t="shared" ref="O5" si="6">IFERROR(K5/H5-1,"")</f>
-        <v>-2.3346057986560753E-3</v>
+        <f t="shared" si="5"/>
+        <v>0.24889518886016848</v>
       </c>
       <c r="P5" s="12" t="str">
-        <f t="shared" ref="P5" si="7">IFERROR(L5/J5-1,"")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="11">
-        <f t="shared" ref="Q5" si="8">IFERROR(N5-M5,"")</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q5" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
       </c>
       <c r="R5" s="12" t="str">
-        <f t="shared" ref="R5" si="9">IFERROR(N5/M5-1,"")</f>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="S5" s="12">
@@ -1579,70 +1579,59 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>51</v>
+        <v>211</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>52</v>
+        <v>210</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="H6" s="8">
-        <v>212.15</v>
+        <v>292.97000000000003</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="9">
-        <v>1</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="J6" s="9"/>
       <c r="K6" s="8">
-        <v>377.4</v>
-      </c>
-      <c r="L6" s="13">
-        <f>IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
-      </c>
-      <c r="M6" s="11">
-        <f t="shared" si="0"/>
-        <v>26518.75</v>
-      </c>
-      <c r="N6" s="11">
-        <f t="shared" si="1"/>
-        <v>47175</v>
-      </c>
+        <v>316.23</v>
+      </c>
+      <c r="L6" s="13"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
       <c r="O6" s="12">
-        <f t="shared" si="5"/>
-        <v>0.77893000235682286</v>
-      </c>
-      <c r="P6" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="O6" si="6">IFERROR(K6/H6-1,"")</f>
+        <v>7.9393794586476441E-2</v>
+      </c>
+      <c r="P6" s="12" t="str">
+        <f t="shared" ref="P6" si="7">IFERROR(L6/J6-1,"")</f>
+        <v/>
       </c>
       <c r="Q6" s="11">
-        <f t="shared" si="3"/>
-        <v>20656.25</v>
-      </c>
-      <c r="R6" s="12">
-        <f t="shared" si="4"/>
-        <v>0.77893000235682308</v>
+        <f t="shared" ref="Q6" si="8">IFERROR(N6-M6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="12" t="str">
+        <f t="shared" ref="R6" si="9">IFERROR(N6/M6-1,"")</f>
+        <v/>
       </c>
       <c r="S6" s="12">
         <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>6.3600573032062777E-2</v>
+        <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="U6" s="6" t="s">
         <v>35</v>
@@ -1665,68 +1654,70 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="H7" s="8">
-        <v>47.25</v>
+        <v>212.15</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J7" s="9">
+        <v>1</v>
+      </c>
       <c r="K7" s="8">
-        <v>40</v>
-      </c>
-      <c r="L7" s="13" t="str">
-        <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
+        <v>377.4</v>
+      </c>
+      <c r="L7" s="13">
+        <f>IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>26518.75</v>
+      </c>
+      <c r="N7" s="11">
+        <f t="shared" si="1"/>
+        <v>47175</v>
       </c>
       <c r="O7" s="12">
         <f t="shared" si="5"/>
-        <v>-0.15343915343915349</v>
-      </c>
-      <c r="P7" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q7" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R7" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>0.77893000235682286</v>
+      </c>
+      <c r="P7" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11">
+        <f t="shared" si="3"/>
+        <v>20656.25</v>
+      </c>
+      <c r="R7" s="12">
+        <f t="shared" si="4"/>
+        <v>0.77893000235682308</v>
       </c>
       <c r="S7" s="12">
         <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0</v>
+        <v>6.3600573032062777E-2</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="U7" s="6" t="s">
         <v>35</v>
@@ -1749,33 +1740,33 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="7">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="H8" s="8">
-        <v>394.77</v>
+        <v>47.25</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8">
-        <v>425</v>
+        <v>40</v>
       </c>
       <c r="L8" s="13" t="str">
         <f ca="1">IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1791,7 +1782,7 @@
       </c>
       <c r="O8" s="12">
         <f t="shared" si="5"/>
-        <v>7.6576234262988541E-2</v>
+        <v>-0.15343915343915349</v>
       </c>
       <c r="P8" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1810,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="U8" s="6" t="s">
         <v>35</v>
@@ -1833,70 +1824,68 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="7">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="H9" s="8">
-        <v>405.68</v>
+        <v>394.77</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="9">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="J9" s="9"/>
       <c r="K9" s="8">
-        <v>910</v>
-      </c>
-      <c r="L9" s="13">
-        <f>IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>425</v>
+      </c>
+      <c r="L9" s="13" t="str">
+        <f ca="1">IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M9" s="11">
         <f t="shared" si="0"/>
-        <v>25557.84</v>
-      </c>
-      <c r="N9" s="11">
-        <f t="shared" si="1"/>
-        <v>57330</v>
+        <v>0</v>
+      </c>
+      <c r="N9" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="5"/>
-        <v>1.2431473082232301</v>
-      </c>
-      <c r="P9" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <f t="shared" si="3"/>
-        <v>31772.16</v>
-      </c>
-      <c r="R9" s="12">
-        <f t="shared" si="4"/>
-        <v>1.2431473082232301</v>
+        <v>7.6576234262988541E-2</v>
+      </c>
+      <c r="P9" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q9" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R9" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S9" s="12">
         <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>7.7291380009075969E-2</v>
+        <v>0</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="U9" s="6" t="s">
         <v>35</v>
@@ -1919,26 +1908,26 @@
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7">
-        <v>396</v>
+        <v>63</v>
       </c>
       <c r="H10" s="8">
-        <v>433</v>
+        <v>405.68</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>42</v>
@@ -1947,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>298</v>
+        <v>910</v>
       </c>
       <c r="L10" s="13">
         <f>IF(I10="DKK",1,IFERROR(_xludf.XLOOKUP(I10,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1955,15 +1944,15 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="0"/>
-        <v>171468</v>
+        <v>25557.84</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>118008</v>
+        <v>57330</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="5"/>
-        <v>-0.31177829099307164</v>
+        <v>1.2431473082232301</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1971,18 +1960,18 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>-53460</v>
+        <v>31772.16</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>-0.31177829099307164</v>
+        <v>1.2431473082232301</v>
       </c>
       <c r="S10" s="12">
         <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0.1590964795414449</v>
+        <v>7.7291380009075969E-2</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="U10" s="6" t="s">
         <v>35</v>
@@ -2005,26 +1994,26 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>33</v>
+        <v>396</v>
       </c>
       <c r="H11" s="8">
-        <v>710.62</v>
+        <v>433</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>42</v>
@@ -2033,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="8">
-        <v>846.8</v>
+        <v>298</v>
       </c>
       <c r="L11" s="13">
         <f>IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2041,15 +2030,15 @@
       </c>
       <c r="M11" s="11">
         <f t="shared" si="0"/>
-        <v>23450.46</v>
+        <v>171468</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>27944.399999999998</v>
+        <v>118008</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="5"/>
-        <v>0.19163547324871222</v>
+        <v>-0.31177829099307164</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="2"/>
@@ -2057,18 +2046,18 @@
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>4493.9399999999987</v>
+        <v>-53460</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="4"/>
-        <v>0.19163547324871244</v>
+        <v>-0.31177829099307164</v>
       </c>
       <c r="S11" s="12">
         <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>3.7674188723628502E-2</v>
+        <v>0.1590964795414449</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>35</v>
@@ -2091,59 +2080,70 @@
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H12" s="8">
-        <v>123.66</v>
+        <v>710.62</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J12" s="9">
+        <v>1</v>
+      </c>
       <c r="K12" s="8">
-        <v>110.8</v>
-      </c>
-      <c r="L12" s="13"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
+        <v>846.8</v>
+      </c>
+      <c r="L12" s="13">
+        <f>IF(I12="DKK",1,IFERROR(_xludf.XLOOKUP(I12,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="11">
+        <f t="shared" si="0"/>
+        <v>23450.46</v>
+      </c>
+      <c r="N12" s="11">
+        <f t="shared" si="1"/>
+        <v>27944.399999999998</v>
+      </c>
       <c r="O12" s="12">
-        <f>IFERROR(K12/H12-1,"")</f>
-        <v>-0.10399482451884201</v>
-      </c>
-      <c r="P12" s="12" t="str">
-        <f>IFERROR(L12/J12-1,"")</f>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>0.19163547324871222</v>
+      </c>
+      <c r="P12" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Q12" s="11">
-        <f>IFERROR(N12-M12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="12" t="str">
-        <f>IFERROR(N12/M12-1,"")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>4493.9399999999987</v>
+      </c>
+      <c r="R12" s="12">
+        <f t="shared" si="4"/>
+        <v>0.19163547324871244</v>
       </c>
       <c r="S12" s="12">
         <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0</v>
+        <v>3.7674188723628502E-2</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>35</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>29</v>
@@ -2182,10 +2182,10 @@
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H13" s="8">
-        <v>139.62</v>
+        <v>137.86000000000001</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>48</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="5"/>
-        <v>0.12963758773814638</v>
+        <v>0.14405919048309856</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>29</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7">
@@ -2397,7 +2397,7 @@
         <v>2.4754273270933991E-2</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>35</v>
@@ -2420,19 +2420,19 @@
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>93</v>
-      </c>
       <c r="D16" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U16" s="6" t="s">
         <v>35</v>
@@ -2500,25 +2500,25 @@
       </c>
       <c r="Z16" s="6"/>
       <c r="AA16" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB16" s="14"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="D17" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
@@ -2590,19 +2590,19 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="E18" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7">
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>35</v>
@@ -2674,19 +2674,19 @@
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
@@ -2714,7 +2714,7 @@
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
       <c r="T19" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>35</v>
@@ -2737,19 +2737,19 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C20" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="E20" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7">
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>35</v>
@@ -2821,19 +2821,19 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="E21" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
@@ -2905,19 +2905,19 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="14" t="s">
+      <c r="D22" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="E22" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>35</v>
@@ -2989,19 +2989,19 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="D23" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7">
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>35</v>
@@ -3073,19 +3073,19 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
@@ -3157,19 +3157,19 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="E25" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>35</v>
@@ -3241,19 +3241,19 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="14" t="s">
+      <c r="D26" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="E26" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U26" s="6" t="s">
         <v>35</v>
@@ -3325,19 +3325,19 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>35</v>
@@ -3409,19 +3409,19 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="E28" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
@@ -3470,10 +3470,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="U28" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="U28" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="V28" s="10" t="b">
         <v>1</v>
@@ -3493,19 +3493,19 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="6" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
@@ -3539,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="U29" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="V29" s="10" t="b">
         <v>1</v>
@@ -3562,19 +3562,19 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="6" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7">
@@ -3629,7 +3629,7 @@
         <v>58</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="V30" s="10" t="b">
         <v>0</v>
@@ -3681,16 +3681,16 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>27</v>
@@ -3701,7 +3701,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3715,13 +3715,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>1</v>
@@ -3732,22 +3732,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" t="s">
         <v>144</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>145</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -3772,150 +3772,150 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" t="s">
         <v>151</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>152</v>
-      </c>
-      <c r="D2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3" s="5">
         <v>0.02</v>
       </c>
       <c r="C3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" t="s">
         <v>155</v>
-      </c>
-      <c r="D3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B5" s="5">
         <v>0.25</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B6" s="5">
         <v>0.25</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B7" s="5">
         <v>0.2</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B8" s="5">
         <v>0.2</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" s="5">
         <v>0.1</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" t="s">
         <v>165</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>166</v>
-      </c>
-      <c r="D10" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" t="s">
         <v>169</v>
-      </c>
-      <c r="D11" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3954,19 +3954,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>176</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3995,13 +3995,13 @@
       </c>
       <c r="B3" s="3"/>
       <c r="D3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>178</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4010,13 +4010,13 @@
       </c>
       <c r="B4" s="3"/>
       <c r="D4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>178</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4025,73 +4025,73 @@
       </c>
       <c r="B5" s="3"/>
       <c r="D5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>178</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B6" s="3"/>
       <c r="D6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>178</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>178</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>178</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>178</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4112,7 +4112,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -4131,16 +4131,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4151,16 +4151,16 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4171,16 +4171,16 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4191,505 +4191,525 @@
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>210</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>188</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>191</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>190</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
         <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
         <v>191</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>204</v>
+      </c>
+      <c r="C18" t="s">
+        <v>190</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>201</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
+        <v>187</v>
+      </c>
+      <c r="F31" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" t="s">
         <v>42</v>
       </c>
-      <c r="E31" t="s">
-        <v>188</v>
-      </c>
-      <c r="F31" t="s">
-        <v>177</v>
+      <c r="E32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4734,16 +4754,16 @@
         <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>27</v>
@@ -4751,13 +4771,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" t="s">
         <v>207</v>
-      </c>
-      <c r="B2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C2" t="s">
-        <v>209</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -4769,7 +4789,7 @@
         <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -4808,19 +4828,19 @@
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="F1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4831,14 +4851,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>138602</v>
+        <v>121657</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>138602</v>
+        <v>121657</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6399DF8C-2FAA-40A5-9B5D-77809B45B831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16575DF6-6415-46F5-8885-5A4D3392A070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="221">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -699,6 +699,9 @@
   </si>
   <si>
     <t>MIL</t>
+  </si>
+  <si>
+    <t>GOOG:XMIL</t>
   </si>
 </sst>
 </file>
@@ -1362,10 +1365,10 @@
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="7">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="H3" s="8">
-        <v>493.03</v>
+        <v>532.6</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>42</v>
@@ -1382,15 +1385,15 @@
       </c>
       <c r="M3" s="11">
         <f t="shared" si="0"/>
-        <v>31553.919999999998</v>
+        <v>41542.800000000003</v>
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>40800</v>
+        <v>49725</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O30" si="5">IFERROR(K3/H3-1,"")</f>
-        <v>0.29302476522726817</v>
+        <v>0.19695831768681926</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1398,15 +1401,15 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>9246.0800000000017</v>
+        <v>8182.1999999999971</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.29302476522726817</v>
+        <v>0.19695831768681926</v>
       </c>
       <c r="S3" s="12">
         <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>5.5005901000702934E-2</v>
+        <v>6.725578541772842E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1441,10 +1444,10 @@
         <v>216</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="7">
@@ -1552,7 +1555,7 @@
         <v/>
       </c>
       <c r="S5" s="12">
-        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ref="S5:S18" ca="1" si="6">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1611,23 +1614,23 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="12">
-        <f t="shared" ref="O6" si="6">IFERROR(K6/H6-1,"")</f>
+        <f t="shared" ref="O6" si="7">IFERROR(K6/H6-1,"")</f>
         <v>7.9393794586476441E-2</v>
       </c>
       <c r="P6" s="12" t="str">
-        <f t="shared" ref="P6" si="7">IFERROR(L6/J6-1,"")</f>
+        <f t="shared" ref="P6" si="8">IFERROR(L6/J6-1,"")</f>
         <v/>
       </c>
       <c r="Q6" s="11">
-        <f t="shared" ref="Q6" si="8">IFERROR(N6-M6,"")</f>
+        <f t="shared" ref="Q6" si="9">IFERROR(N6-M6,"")</f>
         <v>0</v>
       </c>
       <c r="R6" s="12" t="str">
-        <f t="shared" ref="R6" si="9">IFERROR(N6/M6-1,"")</f>
+        <f t="shared" ref="R6" si="10">IFERROR(N6/M6-1,"")</f>
         <v/>
       </c>
       <c r="S6" s="12">
-        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1670,10 +1673,10 @@
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="H7" s="8">
-        <v>212.15</v>
+        <v>223.99</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>42</v>
@@ -1690,15 +1693,15 @@
       </c>
       <c r="M7" s="11">
         <f t="shared" si="0"/>
-        <v>26518.75</v>
+        <v>21279.05</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="1"/>
-        <v>47175</v>
+        <v>35853</v>
       </c>
       <c r="O7" s="12">
         <f t="shared" si="5"/>
-        <v>0.77893000235682286</v>
+        <v>0.68489664717174858</v>
       </c>
       <c r="P7" s="12">
         <f t="shared" si="2"/>
@@ -1706,15 +1709,15 @@
       </c>
       <c r="Q7" s="11">
         <f t="shared" si="3"/>
-        <v>20656.25</v>
+        <v>14573.95</v>
       </c>
       <c r="R7" s="12">
         <f t="shared" si="4"/>
-        <v>0.77893000235682308</v>
+        <v>0.68489664717174881</v>
       </c>
       <c r="S7" s="12">
-        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>6.3600573032062777E-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>4.8493145793500593E-2</v>
       </c>
       <c r="T7" s="6" t="s">
         <v>43</v>
@@ -1797,7 +1800,7 @@
         <v/>
       </c>
       <c r="S8" s="12">
-        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1881,7 +1884,7 @@
         <v/>
       </c>
       <c r="S9" s="12">
-        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1967,8 +1970,8 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S10" s="12">
-        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>7.7291380009075969E-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>7.7541964363969235E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>58</v>
@@ -2053,8 +2056,8 @@
         <v>-0.31177829099307164</v>
       </c>
       <c r="S11" s="12">
-        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0.1590964795414449</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0.15961228206285158</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>69</v>
@@ -2139,8 +2142,8 @@
         <v>0.19163547324871244</v>
       </c>
       <c r="S12" s="12">
-        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>3.7674188723628502E-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>3.7796331222265854E-2</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>74</v>
@@ -2223,7 +2226,7 @@
         <v/>
       </c>
       <c r="S13" s="12">
-        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2307,7 +2310,7 @@
         <v/>
       </c>
       <c r="S14" s="12">
-        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -2393,8 +2396,8 @@
         <v>0.13362013612430967</v>
       </c>
       <c r="S15" s="12">
-        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>2.4754273270933991E-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2.4834528450718853E-2</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>89</v>
@@ -2477,7 +2480,7 @@
         <v/>
       </c>
       <c r="S16" s="12">
-        <f ca="1">IF(W16=TRUE,IFERROR(N16/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -2563,7 +2566,7 @@
         <v/>
       </c>
       <c r="S17" s="12">
-        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -2647,7 +2650,7 @@
         <v/>
       </c>
       <c r="S18" s="12">
-        <f ca="1">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -2794,7 +2797,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ref="S20:S30" ca="1" si="11">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2878,7 +2881,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2962,7 +2965,7 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -3046,7 +3049,7 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -3130,7 +3133,7 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3214,7 +3217,7 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3298,7 +3301,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3382,7 +3385,7 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -3466,7 +3469,7 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -3535,7 +3538,7 @@
       <c r="Q29" s="11"/>
       <c r="R29" s="12"/>
       <c r="S29" s="12">
-        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -3622,8 +3625,8 @@
         <v>1.609105180533752</v>
       </c>
       <c r="S30" s="12">
-        <f ca="1">IF(W30=TRUE,IFERROR(N30/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0.58257720442215077</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>0.58446596268896533</v>
       </c>
       <c r="T30" s="6" t="s">
         <v>58</v>
